--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="887">
   <si>
     <t>id</t>
   </si>
@@ -66,15 +66,126 @@
     <t>sort_order</t>
   </si>
   <si>
+    <t>Lê Tố Uyên (Lúa )</t>
+  </si>
+  <si>
+    <t>Uyên</t>
+  </si>
+  <si>
+    <t>Thành viên</t>
+  </si>
+  <si>
+    <t>Thành viên mới</t>
+  </si>
+  <si>
+    <t>🌾</t>
+  </si>
+  <si>
+    <t>./public/member-images/2026/LE_TO_UYEN.webp</t>
+  </si>
+  <si>
+    <t>Trần Thị Anh Thư</t>
+  </si>
+  <si>
+    <t>Thư</t>
+  </si>
+  <si>
+    <t>☘️</t>
+  </si>
+  <si>
+    <t>./public/member-images/2026/TRAN_THI_ANH_THU.webp</t>
+  </si>
+  <si>
+    <t>Đặng Ngọc Ánh (linda, éng)</t>
+  </si>
+  <si>
+    <t>Ánh</t>
+  </si>
+  <si>
+    <t>Clarie</t>
+  </si>
+  <si>
+    <t>./public/member-images/2026/DANG_NGOC_ANH.webp</t>
+  </si>
+  <si>
+    <t>Lê Thị Mận (Mân)</t>
+  </si>
+  <si>
+    <t>Mận</t>
+  </si>
+  <si>
+    <t>Lê Mân</t>
+  </si>
+  <si>
+    <t>./public/member-images/2026/LE_THI_MAN.webp</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thảo Ly (Cún)</t>
+  </si>
+  <si>
+    <t>Ly</t>
+  </si>
+  <si>
+    <t>./public/member-images/2026/NGUYEN_THI_THAO_LY.webp</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Mỹ Thanh Ngân</t>
+  </si>
+  <si>
+    <t>Ngân</t>
+  </si>
+  <si>
+    <t>Ngân Thanh</t>
+  </si>
+  <si>
+    <t>./public/member-images/2026/NGUYEN_THI_MY_THANH_NGAN.webp</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Bình An (Tùng)</t>
+  </si>
+  <si>
+    <t>An</t>
+  </si>
+  <si>
+    <t>Tung shahur</t>
+  </si>
+  <si>
+    <t>./public/member-images/2026/NGUYEN_HUU_BINH_AN.webp</t>
+  </si>
+  <si>
+    <t>Lê Văn Tài</t>
+  </si>
+  <si>
+    <t>Tài</t>
+  </si>
+  <si>
+    <t>./public/member-images/2026/LE_VAN_TAI.webp</t>
+  </si>
+  <si>
+    <t>Hồ Mỹ Lâm Uyên</t>
+  </si>
+  <si>
+    <t>./public/member-images/2026/HO_MY_LAM_UYEN.webp</t>
+  </si>
+  <si>
+    <t>Nguyễn Quý Khánh Minh</t>
+  </si>
+  <si>
+    <t>Minh</t>
+  </si>
+  <si>
+    <t>min vina</t>
+  </si>
+  <si>
+    <t>./public/member-images/2026/NGUYEN_QUY_KHANH_MINH.webp</t>
+  </si>
+  <si>
     <t>Lê Thị Thuỳ Trang</t>
   </si>
   <si>
     <t>Trang</t>
   </si>
   <si>
-    <t>Thành viên</t>
-  </si>
-  <si>
     <t>Tương Sinh</t>
   </si>
   <si>
@@ -102,9 +213,6 @@
     <t>Hoàng Ngọc Hoài An</t>
   </si>
   <si>
-    <t>An</t>
-  </si>
-  <si>
     <t>Nắng Yêu Thương</t>
   </si>
   <si>
@@ -144,9 +252,6 @@
     <t>Nguyễn Nhật Ánh (Tia)</t>
   </si>
   <si>
-    <t>Ánh</t>
-  </si>
-  <si>
     <t>Tia Nắng</t>
   </si>
   <si>
@@ -180,12 +285,6 @@
     <t>./public/member-images/2025/LE_BAO_TRAN.webp</t>
   </si>
   <si>
-    <t>Trần Thị Anh Thư</t>
-  </si>
-  <si>
-    <t>Thư</t>
-  </si>
-  <si>
     <t>Niệm vô thất</t>
   </si>
   <si>
@@ -210,9 +309,6 @@
     <t>Lê Thị Trà My</t>
   </si>
   <si>
-    <t>☘️</t>
-  </si>
-  <si>
     <t>Hồ Thị Minh Châu (cún)</t>
   </si>
   <si>
@@ -265,9 +361,6 @@
   </si>
   <si>
     <t>Nguyễn Phan Bảo Uyên</t>
-  </si>
-  <si>
-    <t>Uyên</t>
   </si>
   <si>
     <t>🧶</t>
@@ -413,9 +506,6 @@
     <t>Nguyễn Hồ Minh Anh (Manh)</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Nguyễn Hoàng Quỳnh Như</t>
   </si>
   <si>
@@ -557,9 +647,6 @@
     <t>Huỳnh Tuấn Minh</t>
   </si>
   <si>
-    <t>Minh</t>
-  </si>
-  <si>
     <t>Đặng Thị Khánh Linh</t>
   </si>
   <si>
@@ -636,9 +723,6 @@
   </si>
   <si>
     <t>Nguyễn Anh Tài (Tài Cris)</t>
-  </si>
-  <si>
-    <t>Tài</t>
   </si>
   <si>
     <t>Siêu đầu bếp Chánh Tâm</t>
@@ -1231,9 +1315,6 @@
     <t>Nguyễn Thị Thu Ngân</t>
   </si>
   <si>
-    <t>Ngân</t>
-  </si>
-  <si>
     <t>Quảng Diệu</t>
   </si>
   <si>
@@ -1291,6 +1372,9 @@
     <t>Thuỳ</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>./public/member-images/2023/NGUYEN_THI_THUY.webp</t>
   </si>
   <si>
@@ -1433,9 +1517,6 @@
   </si>
   <si>
     <t>Trần Thị Ly (lixinh)</t>
-  </si>
-  <si>
-    <t>Ly</t>
   </si>
   <si>
     <t>./public/member-images/2023/TRAN_THI_LY.webp</t>
@@ -2985,7 +3066,7 @@
     <col customWidth="1" min="4" max="4" width="21.44"/>
     <col customWidth="1" min="5" max="5" width="15.78"/>
     <col customWidth="1" min="6" max="6" width="46.78"/>
-    <col customWidth="1" min="7" max="7" width="39.0"/>
+    <col customWidth="1" min="7" max="7" width="41.89"/>
     <col customWidth="1" min="8" max="26" width="8.56"/>
   </cols>
   <sheetData>
@@ -3015,16 +3096,263 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1"/>
-    <row r="3" ht="15.75" customHeight="1"/>
-    <row r="4" ht="15.75" customHeight="1"/>
-    <row r="5" ht="15.75" customHeight="1"/>
-    <row r="6" ht="15.75" customHeight="1"/>
-    <row r="7" ht="15.75" customHeight="1"/>
-    <row r="8" ht="15.75" customHeight="1"/>
-    <row r="9" ht="15.75" customHeight="1"/>
-    <row r="10" ht="15.75" customHeight="1"/>
-    <row r="11" ht="15.75" customHeight="1"/>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>
@@ -4070,22 +4398,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>671</v>
+        <v>698</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>672</v>
+        <v>699</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>673</v>
+        <v>700</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>674</v>
+        <v>701</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -4096,22 +4424,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>675</v>
+        <v>702</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>676</v>
+        <v>703</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>593</v>
+        <v>620</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>677</v>
+        <v>704</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>678</v>
+        <v>705</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>679</v>
+        <v>706</v>
       </c>
       <c r="H3" s="2">
         <v>2.0</v>
@@ -4122,22 +4450,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>680</v>
+        <v>707</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>681</v>
+        <v>708</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>682</v>
+        <v>709</v>
       </c>
       <c r="H4" s="2">
         <v>6.0</v>
@@ -4148,22 +4476,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>683</v>
+        <v>710</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>684</v>
+        <v>711</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>685</v>
+        <v>712</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>686</v>
+        <v>713</v>
       </c>
       <c r="H5" s="1">
         <v>3.0</v>
@@ -4174,22 +4502,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>687</v>
+        <v>714</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>688</v>
+        <v>715</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>690</v>
+        <v>717</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -4200,22 +4528,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>691</v>
+        <v>718</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>613</v>
+        <v>640</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>692</v>
+        <v>719</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>693</v>
+        <v>720</v>
       </c>
       <c r="H7" s="1">
         <v>6.0</v>
@@ -4226,22 +4554,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>694</v>
+        <v>721</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>695</v>
+        <v>722</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>696</v>
+        <v>723</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>697</v>
+        <v>724</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -4252,22 +4580,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>698</v>
+        <v>725</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>700</v>
+        <v>727</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -5317,22 +5645,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>702</v>
+        <v>729</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>703</v>
+        <v>730</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>688</v>
+        <v>715</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>704</v>
+        <v>731</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>705</v>
+        <v>732</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6387,22 +6715,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>706</v>
+        <v>733</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>539</v>
+        <v>566</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>707</v>
+        <v>734</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>708</v>
+        <v>735</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>709</v>
+        <v>736</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6413,22 +6741,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>710</v>
+        <v>737</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>711</v>
+        <v>738</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>712</v>
+        <v>739</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>713</v>
+        <v>740</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -7482,22 +7810,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>714</v>
+        <v>741</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>715</v>
+        <v>742</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>716</v>
+        <v>743</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>717</v>
+        <v>744</v>
       </c>
       <c r="H2" s="7">
         <v>5.0</v>
@@ -8552,19 +8880,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>718</v>
+        <v>745</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>719</v>
+        <v>746</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>720</v>
+        <v>747</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -8575,19 +8903,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>721</v>
+        <v>748</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>722</v>
+        <v>749</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -9644,22 +9972,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>723</v>
+        <v>750</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>724</v>
+        <v>751</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>725</v>
+        <v>752</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -9670,22 +9998,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>727</v>
+        <v>754</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>730</v>
+        <v>757</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -9696,22 +10024,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>732</v>
+        <v>759</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>733</v>
+        <v>760</v>
       </c>
       <c r="H4" s="2">
         <v>4.0</v>
@@ -9722,22 +10050,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>734</v>
+        <v>761</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>736</v>
+        <v>763</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -10791,22 +11119,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>737</v>
+        <v>764</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>648</v>
+        <v>675</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>738</v>
+        <v>765</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>739</v>
+        <v>766</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -10817,22 +11145,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>740</v>
+        <v>767</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>741</v>
+        <v>768</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>742</v>
+        <v>769</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -10843,22 +11171,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>744</v>
+        <v>771</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>745</v>
+        <v>772</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>746</v>
+        <v>773</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -10869,22 +11197,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>747</v>
+        <v>774</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>748</v>
+        <v>775</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>749</v>
+        <v>776</v>
       </c>
       <c r="H5" s="1">
         <v>6.0</v>
@@ -10895,22 +11223,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>750</v>
+        <v>777</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>751</v>
+        <v>778</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>752</v>
+        <v>779</v>
       </c>
       <c r="H6" s="2">
         <v>6.0</v>
@@ -11933,7 +12261,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -15096,22 +15424,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -15122,22 +15450,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -15148,22 +15476,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -15174,22 +15502,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="H5" s="2">
         <v>9.0</v>
@@ -15200,22 +15528,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -15226,22 +15554,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -15252,22 +15580,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -15278,22 +15606,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -15304,22 +15632,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H10" s="2">
         <v>6.0</v>
@@ -15330,22 +15658,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -15356,19 +15684,19 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -15379,22 +15707,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -15405,22 +15733,22 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="H14" s="2">
         <v>9.0</v>
@@ -16462,22 +16790,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>754</v>
+        <v>781</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>755</v>
+        <v>782</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>757</v>
+        <v>784</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>758</v>
+        <v>785</v>
       </c>
       <c r="H2" s="2">
         <v>8.0</v>
@@ -16488,19 +16816,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>760</v>
+        <v>787</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>755</v>
+        <v>782</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H3" s="2">
         <v>8.0</v>
@@ -16511,22 +16839,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>761</v>
+        <v>788</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>755</v>
+        <v>782</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>762</v>
+        <v>789</v>
       </c>
       <c r="H4" s="2">
         <v>8.0</v>
@@ -16537,19 +16865,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>763</v>
+        <v>790</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>755</v>
+        <v>782</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H5" s="2">
         <v>8.0</v>
@@ -16560,19 +16888,19 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>764</v>
+        <v>791</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>755</v>
+        <v>782</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H6" s="2">
         <v>8.0</v>
@@ -16583,22 +16911,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>765</v>
+        <v>792</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>198</v>
+        <v>38</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>766</v>
+        <v>793</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>767</v>
+        <v>794</v>
       </c>
       <c r="H7" s="2">
         <v>5.0</v>
@@ -16609,22 +16937,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>768</v>
+        <v>795</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>395</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>769</v>
+        <v>796</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -16635,22 +16963,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>770</v>
+        <v>797</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>771</v>
+        <v>798</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -16661,19 +16989,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>773</v>
+        <v>800</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>774</v>
+        <v>801</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H10" s="2">
         <v>7.0</v>
@@ -16684,19 +17012,19 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>775</v>
+        <v>802</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -16707,19 +17035,19 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>776</v>
+        <v>803</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H12" s="2">
         <v>10.0</v>
@@ -16730,19 +17058,19 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>777</v>
+        <v>804</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>778</v>
+        <v>805</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
@@ -16753,19 +17081,19 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>779</v>
+        <v>806</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>780</v>
+        <v>807</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
@@ -16776,19 +17104,19 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>781</v>
+        <v>808</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>782</v>
+        <v>809</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>783</v>
+        <v>810</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
@@ -16799,19 +17127,19 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>784</v>
+        <v>811</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>785</v>
+        <v>812</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
@@ -16822,19 +17150,19 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>786</v>
+        <v>813</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>529</v>
+        <v>556</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
@@ -16845,19 +17173,19 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>787</v>
+        <v>814</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
@@ -16868,19 +17196,19 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>788</v>
+        <v>815</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
@@ -16891,19 +17219,19 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>789</v>
+        <v>816</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
@@ -16914,19 +17242,19 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>790</v>
+        <v>817</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
@@ -16937,19 +17265,19 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>791</v>
+        <v>818</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
@@ -16960,19 +17288,19 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>792</v>
+        <v>819</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
@@ -16983,19 +17311,19 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>793</v>
+        <v>820</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
@@ -17006,19 +17334,19 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>794</v>
+        <v>821</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>795</v>
+        <v>822</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
@@ -17029,19 +17357,19 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>796</v>
+        <v>823</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H26" s="2">
         <v>10.0</v>
@@ -17052,19 +17380,19 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
@@ -17075,19 +17403,19 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>798</v>
+        <v>825</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
@@ -17098,19 +17426,19 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>799</v>
+        <v>826</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
@@ -17121,19 +17449,19 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>800</v>
+        <v>827</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
@@ -17144,19 +17472,19 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>801</v>
+        <v>828</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>802</v>
+        <v>829</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H31" s="2">
         <v>10.0</v>
@@ -17167,19 +17495,19 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>803</v>
+        <v>830</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H32" s="2">
         <v>10.0</v>
@@ -17190,19 +17518,19 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>804</v>
+        <v>831</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
@@ -17213,19 +17541,19 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>805</v>
+        <v>832</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H34" s="2">
         <v>10.0</v>
@@ -17236,19 +17564,19 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>806</v>
+        <v>833</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>523</v>
+        <v>550</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
@@ -17259,19 +17587,19 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>807</v>
+        <v>834</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>808</v>
+        <v>835</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
@@ -17282,19 +17610,19 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>809</v>
+        <v>836</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
@@ -17305,19 +17633,19 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>810</v>
+        <v>837</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>811</v>
+        <v>838</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H38" s="2">
         <v>10.0</v>
@@ -17328,19 +17656,19 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>812</v>
+        <v>839</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
@@ -17351,19 +17679,19 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H40" s="2">
         <v>10.0</v>
@@ -17374,19 +17702,19 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>813</v>
+        <v>840</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
@@ -17397,19 +17725,19 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>814</v>
+        <v>841</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>815</v>
+        <v>842</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
@@ -17420,19 +17748,19 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>816</v>
+        <v>843</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>817</v>
+        <v>844</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H43" s="2">
         <v>10.0</v>
@@ -17443,19 +17771,19 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>818</v>
+        <v>845</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
@@ -17466,19 +17794,19 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>819</v>
+        <v>846</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>820</v>
+        <v>847</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H45" s="2">
         <v>10.0</v>
@@ -17489,19 +17817,19 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>821</v>
+        <v>848</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>822</v>
+        <v>849</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
@@ -17512,19 +17840,19 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>823</v>
+        <v>850</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>484</v>
+        <v>511</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H47" s="2">
         <v>10.0</v>
@@ -17535,19 +17863,19 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>824</v>
+        <v>851</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>825</v>
+        <v>852</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H48" s="2">
         <v>10.0</v>
@@ -17558,19 +17886,19 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>826</v>
+        <v>853</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H49" s="2">
         <v>10.0</v>
@@ -17581,19 +17909,19 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>827</v>
+        <v>854</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H50" s="2">
         <v>10.0</v>
@@ -17604,19 +17932,19 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>828</v>
+        <v>855</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>811</v>
+        <v>838</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H51" s="2">
         <v>10.0</v>
@@ -17627,19 +17955,19 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>829</v>
+        <v>856</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H52" s="2">
         <v>10.0</v>
@@ -17650,19 +17978,19 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>830</v>
+        <v>857</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>831</v>
+        <v>858</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H53" s="2">
         <v>10.0</v>
@@ -17673,19 +18001,19 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>832</v>
+        <v>859</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>833</v>
+        <v>860</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H54" s="2">
         <v>10.0</v>
@@ -17696,19 +18024,19 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>834</v>
+        <v>861</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>835</v>
+        <v>862</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H55" s="2">
         <v>10.0</v>
@@ -17719,19 +18047,19 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>836</v>
+        <v>863</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H56" s="2">
         <v>10.0</v>
@@ -17742,19 +18070,19 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>837</v>
+        <v>864</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>838</v>
+        <v>865</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H57" s="2">
         <v>10.0</v>
@@ -17765,19 +18093,19 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>839</v>
+        <v>866</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>198</v>
+        <v>38</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H58" s="2">
         <v>10.0</v>
@@ -17788,19 +18116,19 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>840</v>
+        <v>867</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H59" s="2">
         <v>10.0</v>
@@ -17811,19 +18139,19 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>841</v>
+        <v>868</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>842</v>
+        <v>869</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G60" s="9"/>
       <c r="H60" s="2">
@@ -17835,19 +18163,19 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>811</v>
+        <v>838</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H61" s="2">
         <v>10.0</v>
@@ -17858,19 +18186,19 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>844</v>
+        <v>871</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H62" s="2">
         <v>10.0</v>
@@ -17881,19 +18209,19 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>845</v>
+        <v>872</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H63" s="2">
         <v>10.0</v>
@@ -17904,19 +18232,19 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>539</v>
+        <v>566</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H64" s="2">
         <v>10.0</v>
@@ -17927,19 +18255,19 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>847</v>
+        <v>874</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>848</v>
+        <v>875</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H65" s="2">
         <v>10.0</v>
@@ -17950,19 +18278,19 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>849</v>
+        <v>876</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H66" s="2">
         <v>10.0</v>
@@ -17973,19 +18301,19 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>850</v>
+        <v>877</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H67" s="2">
         <v>10.0</v>
@@ -17996,19 +18324,19 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H68" s="2">
         <v>10.0</v>
@@ -18019,19 +18347,19 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>852</v>
+        <v>879</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>853</v>
+        <v>880</v>
       </c>
       <c r="H69" s="2">
         <v>10.0</v>
@@ -18042,19 +18370,19 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>395</v>
+        <v>30</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H70" s="2">
         <v>10.0</v>
@@ -18065,19 +18393,19 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>855</v>
+        <v>882</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>503</v>
+        <v>530</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H71" s="2">
         <v>10.0</v>
@@ -18088,19 +18416,19 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>856</v>
+        <v>883</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>785</v>
+        <v>812</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H72" s="2">
         <v>10.0</v>
@@ -18111,19 +18439,19 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>857</v>
+        <v>884</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H73" s="2">
         <v>10.0</v>
@@ -18134,19 +18462,19 @@
         <v>73.0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>858</v>
+        <v>885</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H74" s="2">
         <v>10.0</v>
@@ -18157,19 +18485,19 @@
         <v>74.0</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>859</v>
+        <v>886</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>484</v>
+        <v>511</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H75" s="2">
         <v>10.0</v>
@@ -18233,22 +18561,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="H2" s="1">
         <v>4.0</v>
@@ -18259,22 +18587,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -18285,22 +18613,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -18311,22 +18639,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -18337,22 +18665,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
@@ -18363,19 +18691,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="H7" s="1">
         <v>4.0</v>
@@ -18386,22 +18714,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="H8" s="1">
         <v>4.0</v>
@@ -18412,22 +18740,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="H9" s="1">
         <v>4.0</v>
@@ -18438,22 +18766,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="H10" s="1">
         <v>4.0</v>
@@ -18464,22 +18792,22 @@
         <v>12.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="H11" s="2">
         <v>3.0</v>
@@ -18490,22 +18818,22 @@
         <v>31.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="H12" s="2">
         <v>4.0</v>
@@ -18516,22 +18844,22 @@
         <v>78.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -18542,22 +18870,22 @@
         <v>10.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="H14" s="2">
         <v>9.0</v>
@@ -18568,22 +18896,22 @@
         <v>11.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="H15" s="2">
         <v>6.0</v>
@@ -18594,22 +18922,22 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="H16" s="2">
         <v>6.0</v>
@@ -18620,19 +18948,19 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>123</v>
+        <v>62</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H17" s="2">
         <v>9.0</v>
@@ -18643,22 +18971,22 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="H18" s="2">
         <v>6.0</v>
@@ -18669,22 +18997,22 @@
         <v>16.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -18695,22 +19023,22 @@
         <v>17.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -18721,22 +19049,22 @@
         <v>18.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -18747,22 +19075,22 @@
         <v>19.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -18773,22 +19101,22 @@
         <v>20.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="H23" s="2">
         <v>6.0</v>
@@ -18799,19 +19127,19 @@
         <v>21.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>123</v>
+        <v>85</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -18822,19 +19150,19 @@
         <v>22.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>123</v>
+        <v>85</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -18845,19 +19173,19 @@
         <v>23.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>123</v>
+        <v>85</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H26" s="2">
         <v>9.0</v>
@@ -18868,19 +19196,19 @@
         <v>24.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>123</v>
+        <v>85</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -18891,22 +19219,22 @@
         <v>25.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -18917,19 +19245,19 @@
         <v>26.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>123</v>
+        <v>85</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H29" s="2">
         <v>9.0</v>
@@ -18940,19 +19268,19 @@
         <v>27.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>123</v>
+        <v>85</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H30" s="2">
         <v>9.0</v>
@@ -18963,19 +19291,19 @@
         <v>28.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>123</v>
+        <v>85</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H31" s="2">
         <v>9.0</v>
@@ -18986,19 +19314,19 @@
         <v>29.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>123</v>
+        <v>85</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H32" s="2">
         <v>9.0</v>
@@ -19009,22 +19337,22 @@
         <v>30.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -19035,19 +19363,19 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H34" s="2">
         <v>9.0</v>
@@ -19058,19 +19386,19 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H35" s="2">
         <v>9.0</v>
@@ -19081,22 +19409,22 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -19107,19 +19435,19 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H37" s="2">
         <v>9.0</v>
@@ -19130,19 +19458,19 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H38" s="2">
         <v>9.0</v>
@@ -19153,19 +19481,19 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H39" s="2">
         <v>9.0</v>
@@ -19176,19 +19504,19 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H40" s="2">
         <v>9.0</v>
@@ -19199,19 +19527,19 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H41" s="2">
         <v>9.0</v>
@@ -19222,19 +19550,19 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H42" s="2">
         <v>6.0</v>
@@ -19245,19 +19573,19 @@
         <v>41.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H43" s="2">
         <v>9.0</v>
@@ -19268,19 +19596,19 @@
         <v>42.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H44" s="2">
         <v>9.0</v>
@@ -19291,19 +19619,19 @@
         <v>43.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H45" s="2">
         <v>9.0</v>
@@ -19314,19 +19642,19 @@
         <v>44.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H46" s="2">
         <v>6.0</v>
@@ -19337,22 +19665,22 @@
         <v>45.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="H47" s="2">
         <v>9.0</v>
@@ -19363,22 +19691,22 @@
         <v>46.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -19389,22 +19717,22 @@
         <v>47.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>198</v>
+        <v>38</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="H49" s="2">
         <v>6.0</v>
@@ -19415,22 +19743,22 @@
         <v>48.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -19441,22 +19769,22 @@
         <v>49.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="H51" s="2">
         <v>9.0</v>
@@ -19467,22 +19795,22 @@
         <v>50.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="H52" s="2">
         <v>9.0</v>
@@ -19493,19 +19821,19 @@
         <v>51.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="H53" s="2">
         <v>9.0</v>
@@ -19516,19 +19844,19 @@
         <v>52.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="H54" s="2">
         <v>9.0</v>
@@ -19539,19 +19867,19 @@
         <v>53.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="H55" s="2">
         <v>9.0</v>
@@ -19562,22 +19890,22 @@
         <v>54.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="H56" s="2">
         <v>9.0</v>
@@ -19588,19 +19916,19 @@
         <v>55.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="H57" s="2">
         <v>9.0</v>
@@ -19611,22 +19939,22 @@
         <v>56.0</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="H58" s="2">
         <v>9.0</v>
@@ -19637,22 +19965,22 @@
         <v>57.0</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="H59" s="2">
         <v>9.0</v>
@@ -19663,22 +19991,22 @@
         <v>58.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>123</v>
+        <v>74</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="H60" s="2">
         <v>9.0</v>
@@ -19689,22 +20017,22 @@
         <v>59.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>123</v>
+        <v>74</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="H61" s="2">
         <v>9.0</v>
@@ -19715,22 +20043,22 @@
         <v>60.0</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="H62" s="2">
         <v>9.0</v>
@@ -19741,22 +20069,22 @@
         <v>61.0</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="H63" s="2">
         <v>9.0</v>
@@ -19767,22 +20095,22 @@
         <v>62.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>123</v>
+        <v>74</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="H64" s="2">
         <v>9.0</v>
@@ -19793,22 +20121,22 @@
         <v>63.0</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="H65" s="2">
         <v>9.0</v>
@@ -19819,22 +20147,22 @@
         <v>64.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>123</v>
+        <v>74</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="H66" s="2">
         <v>9.0</v>
@@ -19845,22 +20173,22 @@
         <v>65.0</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>247</v>
+        <v>275</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="H67" s="2">
         <v>9.0</v>
@@ -19871,22 +20199,22 @@
         <v>66.0</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="H68" s="2">
         <v>9.0</v>
@@ -19897,22 +20225,22 @@
         <v>67.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="H69" s="2">
         <v>9.0</v>
@@ -19923,22 +20251,22 @@
         <v>68.0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="H70" s="2">
         <v>6.0</v>
@@ -19949,22 +20277,22 @@
         <v>69.0</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>262</v>
+        <v>290</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="H71" s="2">
         <v>6.0</v>
@@ -19975,22 +20303,22 @@
         <v>70.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>265</v>
+        <v>293</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="H72" s="2">
         <v>9.0</v>
@@ -20001,22 +20329,22 @@
         <v>71.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>270</v>
+        <v>298</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="H73" s="2">
         <v>9.0</v>
@@ -20027,19 +20355,19 @@
         <v>72.0</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>123</v>
+        <v>48</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H74" s="2">
         <v>9.0</v>
@@ -20050,19 +20378,19 @@
         <v>73.0</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>123</v>
+        <v>48</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H75" s="2">
         <v>9.0</v>
@@ -20073,22 +20401,22 @@
         <v>74.0</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="H76" s="2">
         <v>6.0</v>
@@ -20099,19 +20427,19 @@
         <v>75.0</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>123</v>
+        <v>48</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H77" s="2">
         <v>9.0</v>
@@ -20122,19 +20450,19 @@
         <v>76.0</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>123</v>
+        <v>48</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="H78" s="2">
         <v>9.0</v>
@@ -20145,19 +20473,19 @@
         <v>77.0</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E79" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="H79" s="2">
         <v>9.0</v>
@@ -20168,22 +20496,22 @@
         <v>78.0</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="H80" s="2">
         <v>9.0</v>
@@ -20194,22 +20522,22 @@
         <v>79.0</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>292</v>
+        <v>320</v>
       </c>
       <c r="H81" s="2">
         <v>9.0</v>
@@ -20220,22 +20548,22 @@
         <v>80.0</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>123</v>
+        <v>74</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="H82" s="2">
         <v>9.0</v>
@@ -20246,22 +20574,22 @@
         <v>81.0</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>296</v>
+        <v>324</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="H83" s="2">
         <v>9.0</v>
@@ -20272,22 +20600,22 @@
         <v>82.0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>123</v>
+        <v>48</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="H84" s="2">
         <v>4.0</v>
@@ -20298,22 +20626,22 @@
         <v>83.0</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>301</v>
+        <v>329</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>304</v>
+        <v>332</v>
       </c>
       <c r="H85" s="2">
         <v>9.0</v>
@@ -20324,22 +20652,22 @@
         <v>84.0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>307</v>
+        <v>335</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="H86" s="2">
         <v>9.0</v>
@@ -20350,22 +20678,22 @@
         <v>85.0</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="H87" s="2">
         <v>9.0</v>
@@ -20376,22 +20704,22 @@
         <v>86.0</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="H88" s="2">
         <v>9.0</v>
@@ -20402,22 +20730,22 @@
         <v>87.0</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="H89" s="2">
         <v>9.0</v>
@@ -20428,22 +20756,22 @@
         <v>88.0</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>319</v>
+        <v>347</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="H90" s="2">
         <v>9.0</v>
@@ -20454,19 +20782,19 @@
         <v>89.0</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="H91" s="2">
         <v>9.0</v>
@@ -21443,22 +21771,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -21469,22 +21797,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -21495,22 +21823,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -21521,22 +21849,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -21547,22 +21875,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
@@ -21573,22 +21901,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="H7" s="2">
         <v>4.0</v>
@@ -21599,22 +21927,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -21625,22 +21953,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -21651,22 +21979,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="H10" s="1">
         <v>5.0</v>
@@ -21677,22 +22005,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -21703,22 +22031,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -21729,22 +22057,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -21755,22 +22083,22 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="H14" s="2">
         <v>6.0</v>
@@ -21781,22 +22109,22 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -21807,22 +22135,22 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -21833,22 +22161,22 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="H17" s="2">
         <v>6.0</v>
@@ -21859,22 +22187,22 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -21885,22 +22213,22 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>383</v>
+        <v>411</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="H19" s="1">
         <v>6.0</v>
@@ -21911,19 +22239,19 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>387</v>
+        <v>415</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>388</v>
+        <v>416</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -21934,22 +22262,22 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -21960,22 +22288,22 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -21986,22 +22314,22 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>395</v>
+        <v>30</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -22012,22 +22340,22 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -22038,22 +22366,22 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -22064,22 +22392,22 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>405</v>
+        <v>432</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>406</v>
+        <v>433</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="H26" s="2">
         <v>3.0</v>
@@ -22090,22 +22418,22 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -22116,22 +22444,22 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -22142,22 +22470,22 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="H29" s="2">
         <v>9.0</v>
@@ -22168,22 +22496,22 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="H30" s="2">
         <v>9.0</v>
@@ -22194,22 +22522,22 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="H31" s="2">
         <v>9.0</v>
@@ -22220,22 +22548,22 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="H32" s="2">
         <v>9.0</v>
@@ -22246,22 +22574,22 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -22272,22 +22600,22 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="H34" s="2">
         <v>9.0</v>
@@ -22298,22 +22626,22 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="H35" s="2">
         <v>9.0</v>
@@ -22324,22 +22652,22 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -22350,22 +22678,22 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>443</v>
+        <v>471</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="H37" s="2">
         <v>9.0</v>
@@ -22376,19 +22704,19 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="H38" s="2">
         <v>9.0</v>
@@ -22399,22 +22727,22 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>450</v>
+        <v>478</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="H39" s="2">
         <v>9.0</v>
@@ -22425,22 +22753,22 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="H40" s="2">
         <v>9.0</v>
@@ -22451,22 +22779,22 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>458</v>
+        <v>486</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>459</v>
+        <v>487</v>
       </c>
       <c r="H41" s="2">
         <v>9.0</v>
@@ -22477,22 +22805,22 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>460</v>
+        <v>488</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>461</v>
+        <v>489</v>
       </c>
       <c r="H42" s="2">
         <v>9.0</v>
@@ -22503,22 +22831,22 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>462</v>
+        <v>490</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>463</v>
+        <v>27</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>464</v>
+        <v>491</v>
       </c>
       <c r="H43" s="2">
         <v>9.0</v>
@@ -22529,19 +22857,19 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H44" s="2">
         <v>9.0</v>
@@ -22552,19 +22880,19 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="H45" s="2">
         <v>6.0</v>
@@ -22575,19 +22903,19 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H46" s="2">
         <v>9.0</v>
@@ -22598,19 +22926,19 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="H47" s="2">
         <v>6.0</v>
@@ -22621,22 +22949,22 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>471</v>
+        <v>498</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -22647,22 +22975,22 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>474</v>
+        <v>501</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>475</v>
+        <v>502</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="H49" s="2">
         <v>9.0</v>
@@ -22673,22 +23001,22 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>477</v>
+        <v>504</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>478</v>
+        <v>505</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -23704,22 +24032,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>479</v>
+        <v>506</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>481</v>
+        <v>508</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>482</v>
+        <v>509</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -23730,22 +24058,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>483</v>
+        <v>510</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>484</v>
+        <v>511</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>485</v>
+        <v>512</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>486</v>
+        <v>513</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -23756,22 +24084,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>488</v>
+        <v>515</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -23782,22 +24110,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>490</v>
+        <v>517</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>491</v>
+        <v>518</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>480</v>
+        <v>507</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>493</v>
+        <v>520</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -23808,22 +24136,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>494</v>
+        <v>521</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>495</v>
+        <v>522</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>496</v>
+        <v>523</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>497</v>
+        <v>524</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -23834,22 +24162,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>498</v>
+        <v>525</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>499</v>
+        <v>526</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>500</v>
+        <v>527</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>501</v>
+        <v>528</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -23860,22 +24188,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>503</v>
+        <v>530</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>504</v>
+        <v>531</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>505</v>
+        <v>532</v>
       </c>
       <c r="H8" s="2">
         <v>4.0</v>
@@ -23886,22 +24214,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>506</v>
+        <v>533</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>509</v>
+        <v>536</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>510</v>
+        <v>537</v>
       </c>
       <c r="H9" s="2">
         <v>6.0</v>
@@ -23912,22 +24240,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>511</v>
+        <v>538</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>265</v>
+        <v>293</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>513</v>
+        <v>540</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -23938,22 +24266,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>514</v>
+        <v>541</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>515</v>
+        <v>542</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>516</v>
+        <v>543</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -23964,22 +24292,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>518</v>
+        <v>545</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>519</v>
+        <v>546</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>520</v>
+        <v>547</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>521</v>
+        <v>548</v>
       </c>
       <c r="H12" s="2">
         <v>5.0</v>
@@ -23990,22 +24318,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>522</v>
+        <v>549</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>523</v>
+        <v>550</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>524</v>
+        <v>551</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>525</v>
+        <v>552</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>526</v>
+        <v>553</v>
       </c>
       <c r="H13" s="2">
         <v>3.0</v>
@@ -24016,19 +24344,19 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>527</v>
+        <v>554</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H14" s="1">
         <v>6.0</v>
@@ -24039,22 +24367,22 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>528</v>
+        <v>555</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>529</v>
+        <v>556</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>531</v>
+        <v>558</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -24065,22 +24393,22 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>532</v>
+        <v>559</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>534</v>
+        <v>561</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>535</v>
+        <v>562</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -24091,22 +24419,22 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>537</v>
+        <v>564</v>
       </c>
       <c r="H17" s="2">
         <v>9.0</v>
@@ -24117,22 +24445,22 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>538</v>
+        <v>565</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>539</v>
+        <v>566</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>540</v>
+        <v>567</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>541</v>
+        <v>568</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -24143,22 +24471,22 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>542</v>
+        <v>569</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>543</v>
+        <v>570</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>544</v>
+        <v>571</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -24169,22 +24497,22 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>495</v>
+        <v>522</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>546</v>
+        <v>573</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>547</v>
+        <v>574</v>
       </c>
       <c r="H20" s="2">
         <v>7.0</v>
@@ -24195,22 +24523,22 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>548</v>
+        <v>575</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>549</v>
+        <v>576</v>
       </c>
       <c r="H21" s="2">
         <v>7.0</v>
@@ -24221,22 +24549,22 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>550</v>
+        <v>577</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>551</v>
+        <v>578</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -24247,19 +24575,19 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>552</v>
+        <v>579</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>553</v>
+        <v>580</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>554</v>
+        <v>581</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -24270,22 +24598,22 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>555</v>
+        <v>582</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>556</v>
+        <v>583</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -24296,22 +24624,22 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>557</v>
+        <v>584</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>558</v>
+        <v>585</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>559</v>
+        <v>586</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -24322,22 +24650,22 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>560</v>
+        <v>587</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>529</v>
+        <v>556</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>561</v>
+        <v>588</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>562</v>
+        <v>589</v>
       </c>
       <c r="H26" s="2">
         <v>9.0</v>
@@ -24348,22 +24676,22 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>563</v>
+        <v>590</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>564</v>
+        <v>591</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>565</v>
+        <v>592</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -25367,7 +25695,7 @@
     <col customWidth="1" min="4" max="4" width="20.11"/>
     <col customWidth="1" min="5" max="5" width="14.33"/>
     <col customWidth="1" min="6" max="6" width="13.56"/>
-    <col customWidth="1" min="7" max="7" width="14.33"/>
+    <col customWidth="1" min="7" max="7" width="28.33"/>
     <col customWidth="1" min="8" max="26" width="8.56"/>
   </cols>
   <sheetData>
@@ -25402,22 +25730,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>566</v>
+        <v>593</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>395</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>567</v>
+        <v>594</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>568</v>
+        <v>595</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -25428,22 +25756,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>569</v>
+        <v>596</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>570</v>
+        <v>597</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>571</v>
+        <v>598</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>572</v>
+        <v>599</v>
       </c>
       <c r="H3" s="2">
         <v>7.0</v>
@@ -25454,22 +25782,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>573</v>
+        <v>600</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>484</v>
+        <v>511</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>499</v>
+        <v>526</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>574</v>
+        <v>601</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>575</v>
+        <v>602</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -25480,22 +25808,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>577</v>
+        <v>604</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>578</v>
+        <v>605</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -25506,22 +25834,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>579</v>
+        <v>606</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>580</v>
+        <v>607</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>581</v>
+        <v>608</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -25532,22 +25860,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>584</v>
+        <v>611</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>585</v>
+        <v>612</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>586</v>
+        <v>613</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -25558,19 +25886,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>587</v>
+        <v>614</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H8" s="2">
         <v>6.0</v>
@@ -25581,22 +25909,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>588</v>
+        <v>615</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>589</v>
+        <v>616</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>590</v>
+        <v>617</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -25607,19 +25935,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>591</v>
+        <v>618</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H10" s="2">
         <v>6.0</v>
@@ -26671,22 +26999,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>592</v>
+        <v>619</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>593</v>
+        <v>620</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>594</v>
+        <v>621</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>595</v>
+        <v>622</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>596</v>
+        <v>623</v>
       </c>
       <c r="H2" s="2">
         <v>2.0</v>
@@ -26697,22 +27025,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>597</v>
+        <v>624</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>584</v>
+        <v>611</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>598</v>
+        <v>625</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>599</v>
+        <v>626</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -26723,22 +27051,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>600</v>
+        <v>627</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>601</v>
+        <v>628</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>584</v>
+        <v>611</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>558</v>
+        <v>585</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>602</v>
+        <v>629</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -26749,22 +27077,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>529</v>
+        <v>556</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>584</v>
+        <v>611</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>604</v>
+        <v>631</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>605</v>
+        <v>632</v>
       </c>
       <c r="H5" s="1">
         <v>5.0</v>
@@ -26775,22 +27103,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>606</v>
+        <v>633</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>480</v>
+        <v>507</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>607</v>
+        <v>634</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>608</v>
+        <v>635</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -26801,22 +27129,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>609</v>
+        <v>636</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>610</v>
+        <v>637</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>611</v>
+        <v>638</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>
@@ -26827,19 +27155,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>612</v>
+        <v>639</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>613</v>
+        <v>640</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -26850,22 +27178,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>614</v>
+        <v>641</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>615</v>
+        <v>642</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -26876,19 +27204,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>616</v>
+        <v>643</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -26899,22 +27227,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>617</v>
+        <v>644</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>618</v>
+        <v>645</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>619</v>
+        <v>646</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -26925,22 +27253,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>620</v>
+        <v>647</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>621</v>
+        <v>648</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>622</v>
+        <v>649</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -26951,22 +27279,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>623</v>
+        <v>650</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>484</v>
+        <v>511</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>624</v>
+        <v>651</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>625</v>
+        <v>652</v>
       </c>
       <c r="H13" s="2">
         <v>9.0</v>
@@ -28014,22 +28342,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>626</v>
+        <v>653</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>627</v>
+        <v>654</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>628</v>
+        <v>655</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>629</v>
+        <v>656</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>630</v>
+        <v>657</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -28040,22 +28368,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>631</v>
+        <v>658</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>632</v>
+        <v>659</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>633</v>
+        <v>660</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>634</v>
+        <v>661</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -28066,22 +28394,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>635</v>
+        <v>662</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>636</v>
+        <v>663</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>637</v>
+        <v>664</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>638</v>
+        <v>665</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -28092,19 +28420,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>639</v>
+        <v>666</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>640</v>
+        <v>667</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>123</v>
+        <v>442</v>
       </c>
       <c r="H5" s="2">
         <v>9.0</v>
@@ -28115,22 +28443,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>641</v>
+        <v>668</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>642</v>
+        <v>669</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>643</v>
+        <v>670</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -28141,22 +28469,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>644</v>
+        <v>671</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>645</v>
+        <v>672</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>646</v>
+        <v>673</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -28167,22 +28495,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>647</v>
+        <v>674</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>648</v>
+        <v>675</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>649</v>
+        <v>676</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>651</v>
+        <v>678</v>
       </c>
       <c r="H8" s="2">
         <v>5.0</v>
@@ -29236,22 +29564,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>652</v>
+        <v>679</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>653</v>
+        <v>680</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>654</v>
+        <v>681</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>655</v>
+        <v>682</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -29262,22 +29590,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>656</v>
+        <v>683</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>657</v>
+        <v>684</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>658</v>
+        <v>685</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>659</v>
+        <v>686</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -29288,19 +29616,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>660</v>
+        <v>687</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>661</v>
+        <v>688</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -29311,22 +29639,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>662</v>
+        <v>689</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>636</v>
+        <v>663</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>663</v>
+        <v>690</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>664</v>
+        <v>691</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -29337,22 +29665,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>665</v>
+        <v>692</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>636</v>
+        <v>663</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>666</v>
+        <v>693</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>667</v>
+        <v>694</v>
       </c>
       <c r="H6" s="2">
         <v>7.0</v>
@@ -29363,22 +29691,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>668</v>
+        <v>695</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>669</v>
+        <v>696</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>670</v>
+        <v>697</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1962" uniqueCount="889">
   <si>
     <t>id</t>
   </si>
@@ -178,6 +178,12 @@
   </si>
   <si>
     <t>./public/member-images/2026/NGUYEN_QUY_KHANH_MINH.webp</t>
+  </si>
+  <si>
+    <t>Nguyễn Quý Tường Minh</t>
+  </si>
+  <si>
+    <t>./public/member-images/2026/NGUYEN_QUY_TUONG_MINH.webp</t>
   </si>
   <si>
     <t>Lê Thị Thuỳ Trang</t>
@@ -3063,9 +3069,9 @@
     <col customWidth="1" min="1" max="1" width="8.56"/>
     <col customWidth="1" min="2" max="2" width="30.33"/>
     <col customWidth="1" min="3" max="3" width="11.44"/>
-    <col customWidth="1" min="4" max="4" width="21.44"/>
+    <col customWidth="1" min="4" max="4" width="12.89"/>
     <col customWidth="1" min="5" max="5" width="15.78"/>
-    <col customWidth="1" min="6" max="6" width="46.78"/>
+    <col customWidth="1" min="6" max="6" width="19.11"/>
     <col customWidth="1" min="7" max="7" width="41.89"/>
     <col customWidth="1" min="8" max="26" width="8.56"/>
   </cols>
@@ -3352,8 +3358,36 @@
       <c r="G11" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1"/>
+      <c r="H11" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>
     <row r="15" ht="15.75" customHeight="1"/>
@@ -4398,22 +4432,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -4424,22 +4458,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="H3" s="2">
         <v>2.0</v>
@@ -4450,22 +4484,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="H4" s="2">
         <v>6.0</v>
@@ -4476,22 +4510,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="H5" s="1">
         <v>3.0</v>
@@ -4502,22 +4536,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -4528,22 +4562,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="H7" s="1">
         <v>6.0</v>
@@ -4554,22 +4588,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -4580,22 +4614,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -5645,22 +5679,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6715,22 +6749,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6741,22 +6775,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -7810,22 +7844,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="H2" s="7">
         <v>5.0</v>
@@ -8880,19 +8914,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -8903,19 +8937,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -9972,22 +10006,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -9998,22 +10032,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -10024,22 +10058,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="H4" s="2">
         <v>4.0</v>
@@ -10050,22 +10084,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -11119,22 +11153,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -11145,22 +11179,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -11171,22 +11205,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -11197,22 +11231,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="H5" s="1">
         <v>6.0</v>
@@ -11223,22 +11257,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="H6" s="2">
         <v>6.0</v>
@@ -12261,7 +12295,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -15424,22 +15458,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -15450,22 +15484,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -15476,7 +15510,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>34</v>
@@ -15485,13 +15519,13 @@
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -15502,22 +15536,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H5" s="2">
         <v>9.0</v>
@@ -15528,22 +15562,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -15554,7 +15588,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>19</v>
@@ -15563,13 +15597,13 @@
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -15580,22 +15614,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -15606,22 +15640,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -15641,13 +15675,13 @@
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H10" s="2">
         <v>6.0</v>
@@ -15658,22 +15692,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -15684,16 +15718,16 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>16</v>
@@ -15707,22 +15741,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -15733,22 +15767,22 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H14" s="2">
         <v>9.0</v>
@@ -16790,22 +16824,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="H2" s="2">
         <v>8.0</v>
@@ -16816,19 +16850,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H3" s="2">
         <v>8.0</v>
@@ -16839,22 +16873,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="H4" s="2">
         <v>8.0</v>
@@ -16865,19 +16899,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H5" s="2">
         <v>8.0</v>
@@ -16888,19 +16922,19 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H6" s="2">
         <v>8.0</v>
@@ -16911,22 +16945,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="H7" s="2">
         <v>5.0</v>
@@ -16937,22 +16971,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -16963,22 +16997,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -16989,19 +17023,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H10" s="2">
         <v>7.0</v>
@@ -17012,19 +17046,19 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -17035,19 +17069,19 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H12" s="2">
         <v>10.0</v>
@@ -17058,19 +17092,19 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
@@ -17081,19 +17115,19 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
@@ -17104,19 +17138,19 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
@@ -17127,19 +17161,19 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
@@ -17150,19 +17184,19 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
@@ -17173,7 +17207,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
@@ -17182,10 +17216,10 @@
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
@@ -17196,19 +17230,19 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
@@ -17219,19 +17253,19 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
@@ -17242,19 +17276,19 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
@@ -17265,19 +17299,19 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
@@ -17288,19 +17322,19 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
@@ -17311,19 +17345,19 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
@@ -17334,19 +17368,19 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
@@ -17357,19 +17391,19 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H26" s="2">
         <v>10.0</v>
@@ -17380,7 +17414,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>34</v>
@@ -17389,10 +17423,10 @@
         <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
@@ -17403,19 +17437,19 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
@@ -17426,19 +17460,19 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
@@ -17449,19 +17483,19 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
@@ -17472,19 +17506,19 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H31" s="2">
         <v>10.0</v>
@@ -17495,19 +17529,19 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H32" s="2">
         <v>10.0</v>
@@ -17518,19 +17552,19 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
@@ -17541,19 +17575,19 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H34" s="2">
         <v>10.0</v>
@@ -17564,19 +17598,19 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
@@ -17587,19 +17621,19 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
@@ -17610,7 +17644,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>43</v>
@@ -17619,10 +17653,10 @@
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
@@ -17633,19 +17667,19 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H38" s="2">
         <v>10.0</v>
@@ -17656,7 +17690,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>34</v>
@@ -17665,10 +17699,10 @@
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
@@ -17679,19 +17713,19 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H40" s="2">
         <v>10.0</v>
@@ -17702,19 +17736,19 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
@@ -17725,19 +17759,19 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
@@ -17748,19 +17782,19 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H43" s="2">
         <v>10.0</v>
@@ -17771,19 +17805,19 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
@@ -17794,19 +17828,19 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H45" s="2">
         <v>10.0</v>
@@ -17817,19 +17851,19 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
@@ -17840,19 +17874,19 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H47" s="2">
         <v>10.0</v>
@@ -17863,19 +17897,19 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H48" s="2">
         <v>10.0</v>
@@ -17886,19 +17920,19 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H49" s="2">
         <v>10.0</v>
@@ -17909,19 +17943,19 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H50" s="2">
         <v>10.0</v>
@@ -17932,19 +17966,19 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H51" s="2">
         <v>10.0</v>
@@ -17955,19 +17989,19 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H52" s="2">
         <v>10.0</v>
@@ -17978,19 +18012,19 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H53" s="2">
         <v>10.0</v>
@@ -18001,19 +18035,19 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H54" s="2">
         <v>10.0</v>
@@ -18024,19 +18058,19 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H55" s="2">
         <v>10.0</v>
@@ -18047,19 +18081,19 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H56" s="2">
         <v>10.0</v>
@@ -18070,19 +18104,19 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H57" s="2">
         <v>10.0</v>
@@ -18093,7 +18127,7 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>38</v>
@@ -18102,10 +18136,10 @@
         <v>10</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H58" s="2">
         <v>10.0</v>
@@ -18116,19 +18150,19 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H59" s="2">
         <v>10.0</v>
@@ -18139,19 +18173,19 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G60" s="9"/>
       <c r="H60" s="2">
@@ -18163,19 +18197,19 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H61" s="2">
         <v>10.0</v>
@@ -18186,19 +18220,19 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H62" s="2">
         <v>10.0</v>
@@ -18209,19 +18243,19 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H63" s="2">
         <v>10.0</v>
@@ -18232,19 +18266,19 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H64" s="2">
         <v>10.0</v>
@@ -18255,19 +18289,19 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H65" s="2">
         <v>10.0</v>
@@ -18278,19 +18312,19 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H66" s="2">
         <v>10.0</v>
@@ -18301,19 +18335,19 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H67" s="2">
         <v>10.0</v>
@@ -18324,19 +18358,19 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H68" s="2">
         <v>10.0</v>
@@ -18347,7 +18381,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>9</v>
@@ -18356,10 +18390,10 @@
         <v>10</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="H69" s="2">
         <v>10.0</v>
@@ -18370,7 +18404,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>30</v>
@@ -18379,10 +18413,10 @@
         <v>10</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H70" s="2">
         <v>10.0</v>
@@ -18393,19 +18427,19 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H71" s="2">
         <v>10.0</v>
@@ -18416,19 +18450,19 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H72" s="2">
         <v>10.0</v>
@@ -18439,19 +18473,19 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H73" s="2">
         <v>10.0</v>
@@ -18462,19 +18496,19 @@
         <v>73.0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H74" s="2">
         <v>10.0</v>
@@ -18485,19 +18519,19 @@
         <v>74.0</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H75" s="2">
         <v>10.0</v>
@@ -18561,22 +18595,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H2" s="1">
         <v>4.0</v>
@@ -18587,22 +18621,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -18613,22 +18647,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -18639,22 +18673,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -18665,22 +18699,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
@@ -18691,19 +18725,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H7" s="1">
         <v>4.0</v>
@@ -18714,22 +18748,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H8" s="1">
         <v>4.0</v>
@@ -18740,22 +18774,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H9" s="1">
         <v>4.0</v>
@@ -18766,22 +18800,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H10" s="1">
         <v>4.0</v>
@@ -18792,22 +18826,22 @@
         <v>12.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H11" s="2">
         <v>3.0</v>
@@ -18818,22 +18852,22 @@
         <v>31.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H12" s="2">
         <v>4.0</v>
@@ -18844,22 +18878,22 @@
         <v>78.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -18870,22 +18904,22 @@
         <v>10.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H14" s="2">
         <v>9.0</v>
@@ -18896,22 +18930,22 @@
         <v>11.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H15" s="2">
         <v>6.0</v>
@@ -18922,22 +18956,22 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H16" s="2">
         <v>6.0</v>
@@ -18948,16 +18982,16 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>16</v>
@@ -18971,22 +19005,22 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H18" s="2">
         <v>6.0</v>
@@ -18997,22 +19031,22 @@
         <v>16.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -19023,22 +19057,22 @@
         <v>17.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -19049,22 +19083,22 @@
         <v>18.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -19075,22 +19109,22 @@
         <v>19.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -19101,22 +19135,22 @@
         <v>20.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H23" s="2">
         <v>6.0</v>
@@ -19127,16 +19161,16 @@
         <v>21.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>16</v>
@@ -19150,16 +19184,16 @@
         <v>22.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>16</v>
@@ -19173,16 +19207,16 @@
         <v>23.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>16</v>
@@ -19196,16 +19230,16 @@
         <v>24.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>16</v>
@@ -19219,22 +19253,22 @@
         <v>25.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -19245,16 +19279,16 @@
         <v>26.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>16</v>
@@ -19268,16 +19302,16 @@
         <v>27.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>16</v>
@@ -19291,16 +19325,16 @@
         <v>28.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>16</v>
@@ -19314,16 +19348,16 @@
         <v>29.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>16</v>
@@ -19337,22 +19371,22 @@
         <v>30.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -19363,16 +19397,16 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>16</v>
@@ -19386,7 +19420,7 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>43</v>
@@ -19395,7 +19429,7 @@
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>16</v>
@@ -19409,22 +19443,22 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -19435,16 +19469,16 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>16</v>
@@ -19458,16 +19492,16 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>16</v>
@@ -19481,16 +19515,16 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>16</v>
@@ -19504,16 +19538,16 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>16</v>
@@ -19527,16 +19561,16 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>16</v>
@@ -19550,16 +19584,16 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>16</v>
@@ -19573,16 +19607,16 @@
         <v>41.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>16</v>
@@ -19596,16 +19630,16 @@
         <v>42.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>16</v>
@@ -19619,7 +19653,7 @@
         <v>43.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>9</v>
@@ -19628,7 +19662,7 @@
         <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>16</v>
@@ -19642,16 +19676,16 @@
         <v>44.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>16</v>
@@ -19665,22 +19699,22 @@
         <v>45.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H47" s="2">
         <v>9.0</v>
@@ -19691,22 +19725,22 @@
         <v>46.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -19717,7 +19751,7 @@
         <v>47.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>38</v>
@@ -19726,13 +19760,13 @@
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H49" s="2">
         <v>6.0</v>
@@ -19743,22 +19777,22 @@
         <v>48.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -19769,22 +19803,22 @@
         <v>49.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H51" s="2">
         <v>9.0</v>
@@ -19795,22 +19829,22 @@
         <v>50.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H52" s="2">
         <v>9.0</v>
@@ -19821,16 +19855,16 @@
         <v>51.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>16</v>
@@ -19844,16 +19878,16 @@
         <v>52.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>16</v>
@@ -19867,16 +19901,16 @@
         <v>53.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>16</v>
@@ -19890,22 +19924,22 @@
         <v>54.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H56" s="2">
         <v>9.0</v>
@@ -19916,16 +19950,16 @@
         <v>55.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>16</v>
@@ -19939,22 +19973,22 @@
         <v>56.0</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H58" s="2">
         <v>9.0</v>
@@ -19965,22 +19999,22 @@
         <v>57.0</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H59" s="2">
         <v>9.0</v>
@@ -19991,22 +20025,22 @@
         <v>58.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H60" s="2">
         <v>9.0</v>
@@ -20017,22 +20051,22 @@
         <v>59.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H61" s="2">
         <v>9.0</v>
@@ -20043,22 +20077,22 @@
         <v>60.0</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H62" s="2">
         <v>9.0</v>
@@ -20069,22 +20103,22 @@
         <v>61.0</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H63" s="2">
         <v>9.0</v>
@@ -20095,22 +20129,22 @@
         <v>62.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H64" s="2">
         <v>9.0</v>
@@ -20121,22 +20155,22 @@
         <v>63.0</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H65" s="2">
         <v>9.0</v>
@@ -20147,22 +20181,22 @@
         <v>64.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H66" s="2">
         <v>9.0</v>
@@ -20173,22 +20207,22 @@
         <v>65.0</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H67" s="2">
         <v>9.0</v>
@@ -20199,22 +20233,22 @@
         <v>66.0</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H68" s="2">
         <v>9.0</v>
@@ -20225,22 +20259,22 @@
         <v>67.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H69" s="2">
         <v>9.0</v>
@@ -20251,7 +20285,7 @@
         <v>68.0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>34</v>
@@ -20260,13 +20294,13 @@
         <v>10</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H70" s="2">
         <v>6.0</v>
@@ -20277,22 +20311,22 @@
         <v>69.0</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H71" s="2">
         <v>6.0</v>
@@ -20303,22 +20337,22 @@
         <v>70.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H72" s="2">
         <v>9.0</v>
@@ -20329,22 +20363,22 @@
         <v>71.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H73" s="2">
         <v>9.0</v>
@@ -20355,16 +20389,16 @@
         <v>72.0</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>16</v>
@@ -20378,16 +20412,16 @@
         <v>73.0</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>16</v>
@@ -20401,22 +20435,22 @@
         <v>74.0</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H76" s="2">
         <v>6.0</v>
@@ -20427,16 +20461,16 @@
         <v>75.0</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>16</v>
@@ -20450,7 +20484,7 @@
         <v>76.0</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>19</v>
@@ -20459,7 +20493,7 @@
         <v>10</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>16</v>
@@ -20473,16 +20507,16 @@
         <v>77.0</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>16</v>
@@ -20496,22 +20530,22 @@
         <v>78.0</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H80" s="2">
         <v>9.0</v>
@@ -20522,22 +20556,22 @@
         <v>79.0</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H81" s="2">
         <v>9.0</v>
@@ -20548,22 +20582,22 @@
         <v>80.0</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H82" s="2">
         <v>9.0</v>
@@ -20574,22 +20608,22 @@
         <v>81.0</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H83" s="2">
         <v>9.0</v>
@@ -20600,22 +20634,22 @@
         <v>82.0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H84" s="2">
         <v>4.0</v>
@@ -20626,22 +20660,22 @@
         <v>83.0</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H85" s="2">
         <v>9.0</v>
@@ -20652,22 +20686,22 @@
         <v>84.0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H86" s="2">
         <v>9.0</v>
@@ -20678,22 +20712,22 @@
         <v>85.0</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H87" s="2">
         <v>9.0</v>
@@ -20704,22 +20738,22 @@
         <v>86.0</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H88" s="2">
         <v>9.0</v>
@@ -20730,22 +20764,22 @@
         <v>87.0</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H89" s="2">
         <v>9.0</v>
@@ -20756,7 +20790,7 @@
         <v>88.0</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>19</v>
@@ -20765,13 +20799,13 @@
         <v>10</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H90" s="2">
         <v>9.0</v>
@@ -20782,16 +20816,16 @@
         <v>89.0</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>16</v>
@@ -21771,22 +21805,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -21797,22 +21831,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -21823,22 +21857,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -21849,22 +21883,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -21875,22 +21909,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
@@ -21901,22 +21935,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H7" s="2">
         <v>4.0</v>
@@ -21927,22 +21961,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -21953,22 +21987,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -21979,22 +22013,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H10" s="1">
         <v>5.0</v>
@@ -22005,22 +22039,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -22031,22 +22065,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -22057,22 +22091,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -22083,22 +22117,22 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H14" s="2">
         <v>6.0</v>
@@ -22109,22 +22143,22 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -22135,22 +22169,22 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -22161,22 +22195,22 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H17" s="2">
         <v>6.0</v>
@@ -22187,22 +22221,22 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -22213,22 +22247,22 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H19" s="1">
         <v>6.0</v>
@@ -22239,19 +22273,19 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -22262,22 +22296,22 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -22288,22 +22322,22 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -22314,7 +22348,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>30</v>
@@ -22323,13 +22357,13 @@
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -22340,22 +22374,22 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -22366,22 +22400,22 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -22392,22 +22426,22 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H26" s="2">
         <v>3.0</v>
@@ -22418,22 +22452,22 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -22444,22 +22478,22 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -22470,22 +22504,22 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H29" s="2">
         <v>9.0</v>
@@ -22496,22 +22530,22 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H30" s="2">
         <v>9.0</v>
@@ -22522,22 +22556,22 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="H31" s="2">
         <v>9.0</v>
@@ -22548,22 +22582,22 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H32" s="2">
         <v>9.0</v>
@@ -22574,22 +22608,22 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -22600,7 +22634,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>43</v>
@@ -22609,13 +22643,13 @@
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="H34" s="2">
         <v>9.0</v>
@@ -22626,22 +22660,22 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="H35" s="2">
         <v>9.0</v>
@@ -22652,22 +22686,22 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -22678,22 +22712,22 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H37" s="2">
         <v>9.0</v>
@@ -22704,19 +22738,19 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="H38" s="2">
         <v>9.0</v>
@@ -22727,22 +22761,22 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H39" s="2">
         <v>9.0</v>
@@ -22753,22 +22787,22 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="H40" s="2">
         <v>9.0</v>
@@ -22779,22 +22813,22 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="H41" s="2">
         <v>9.0</v>
@@ -22805,22 +22839,22 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H42" s="2">
         <v>9.0</v>
@@ -22831,7 +22865,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>27</v>
@@ -22840,13 +22874,13 @@
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H43" s="2">
         <v>9.0</v>
@@ -22857,19 +22891,19 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H44" s="2">
         <v>9.0</v>
@@ -22880,19 +22914,19 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="H45" s="2">
         <v>6.0</v>
@@ -22903,19 +22937,19 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H46" s="2">
         <v>9.0</v>
@@ -22926,19 +22960,19 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="H47" s="2">
         <v>6.0</v>
@@ -22949,22 +22983,22 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -22975,22 +23009,22 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="H49" s="2">
         <v>9.0</v>
@@ -23001,22 +23035,22 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -24032,22 +24066,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -24058,22 +24092,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -24084,22 +24118,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -24110,22 +24144,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -24136,22 +24170,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -24162,22 +24196,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -24188,22 +24222,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H8" s="2">
         <v>4.0</v>
@@ -24214,22 +24248,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="H9" s="2">
         <v>6.0</v>
@@ -24240,22 +24274,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -24266,22 +24300,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -24292,22 +24326,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="H12" s="2">
         <v>5.0</v>
@@ -24318,22 +24352,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H13" s="2">
         <v>3.0</v>
@@ -24344,19 +24378,19 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H14" s="1">
         <v>6.0</v>
@@ -24367,22 +24401,22 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -24393,22 +24427,22 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -24419,22 +24453,22 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H17" s="2">
         <v>9.0</v>
@@ -24445,22 +24479,22 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -24471,22 +24505,22 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -24497,22 +24531,22 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="H20" s="2">
         <v>7.0</v>
@@ -24523,22 +24557,22 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H21" s="2">
         <v>7.0</v>
@@ -24549,22 +24583,22 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -24575,19 +24609,19 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -24598,22 +24632,22 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -24624,22 +24658,22 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -24650,22 +24684,22 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H26" s="2">
         <v>9.0</v>
@@ -24676,22 +24710,22 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -25730,7 +25764,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
@@ -25739,13 +25773,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -25756,22 +25790,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H3" s="2">
         <v>7.0</v>
@@ -25782,22 +25816,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -25808,22 +25842,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -25834,22 +25868,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -25860,22 +25894,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -25886,19 +25920,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H8" s="2">
         <v>6.0</v>
@@ -25909,22 +25943,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -25935,19 +25969,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H10" s="2">
         <v>6.0</v>
@@ -26999,22 +27033,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="H2" s="2">
         <v>2.0</v>
@@ -27025,22 +27059,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -27051,22 +27085,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -27077,22 +27111,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="H5" s="1">
         <v>5.0</v>
@@ -27103,22 +27137,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -27129,22 +27163,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>
@@ -27155,19 +27189,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -27178,22 +27212,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -27204,19 +27238,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -27227,22 +27261,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -27253,22 +27287,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -27279,22 +27313,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="H13" s="2">
         <v>9.0</v>
@@ -28342,22 +28376,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -28368,22 +28402,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -28394,22 +28428,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -28420,19 +28454,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H5" s="2">
         <v>9.0</v>
@@ -28443,22 +28477,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -28469,22 +28503,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -28495,22 +28529,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="H8" s="2">
         <v>5.0</v>
@@ -29564,22 +29598,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -29590,22 +29624,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -29616,19 +29650,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -29639,22 +29673,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -29665,22 +29699,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="H6" s="2">
         <v>7.0</v>
@@ -29691,22 +29725,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1962" uniqueCount="889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="891">
   <si>
     <t>id</t>
   </si>
@@ -186,10 +186,16 @@
     <t>./public/member-images/2026/NGUYEN_QUY_TUONG_MINH.webp</t>
   </si>
   <si>
+    <t>Dương Thị Minh Trang</t>
+  </si>
+  <si>
+    <t>Trang</t>
+  </si>
+  <si>
+    <t>./public/member-images/2026/DUONG_THI_MINH_TRANG.webp</t>
+  </si>
+  <si>
     <t>Lê Thị Thuỳ Trang</t>
-  </si>
-  <si>
-    <t>Trang</t>
   </si>
   <si>
     <t>Tương Sinh</t>
@@ -3388,7 +3394,32 @@
         <v>6.0</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1"/>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
     <row r="14" ht="15.75" customHeight="1"/>
     <row r="15" ht="15.75" customHeight="1"/>
     <row r="16" ht="15.75" customHeight="1"/>
@@ -4432,22 +4463,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -4458,22 +4489,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="H3" s="2">
         <v>2.0</v>
@@ -4484,22 +4515,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H4" s="2">
         <v>6.0</v>
@@ -4510,22 +4541,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="H5" s="1">
         <v>3.0</v>
@@ -4536,22 +4567,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -4562,22 +4593,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H7" s="1">
         <v>6.0</v>
@@ -4588,22 +4619,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -4614,22 +4645,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -5679,22 +5710,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6749,22 +6780,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6775,22 +6806,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -7844,22 +7875,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="H2" s="7">
         <v>5.0</v>
@@ -8914,19 +8945,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -8937,19 +8968,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -10006,22 +10037,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -10032,22 +10063,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -10058,22 +10089,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="H4" s="2">
         <v>4.0</v>
@@ -10084,22 +10115,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -11153,22 +11184,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -11179,22 +11210,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -11205,22 +11236,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -11231,22 +11262,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="H5" s="1">
         <v>6.0</v>
@@ -11257,22 +11288,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="H6" s="2">
         <v>6.0</v>
@@ -12295,7 +12326,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -15458,7 +15489,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>49</v>
@@ -15467,13 +15498,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -15484,22 +15515,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -15510,7 +15541,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>34</v>
@@ -15519,13 +15550,13 @@
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -15536,22 +15567,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H5" s="2">
         <v>9.0</v>
@@ -15562,22 +15593,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -15588,7 +15619,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>19</v>
@@ -15597,13 +15628,13 @@
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -15614,22 +15645,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -15640,22 +15671,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -15675,13 +15706,13 @@
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H10" s="2">
         <v>6.0</v>
@@ -15692,22 +15723,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -15718,16 +15749,16 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>16</v>
@@ -15741,22 +15772,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -15767,22 +15798,22 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2">
         <v>9.0</v>
@@ -16824,22 +16855,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="H2" s="2">
         <v>8.0</v>
@@ -16850,19 +16881,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H3" s="2">
         <v>8.0</v>
@@ -16873,22 +16904,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="H4" s="2">
         <v>8.0</v>
@@ -16899,19 +16930,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H5" s="2">
         <v>8.0</v>
@@ -16922,19 +16953,19 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H6" s="2">
         <v>8.0</v>
@@ -16945,22 +16976,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="H7" s="2">
         <v>5.0</v>
@@ -16971,22 +17002,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -16997,22 +17028,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -17023,19 +17054,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H10" s="2">
         <v>7.0</v>
@@ -17046,19 +17077,19 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -17069,19 +17100,19 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H12" s="2">
         <v>10.0</v>
@@ -17092,19 +17123,19 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
@@ -17115,19 +17146,19 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
@@ -17138,19 +17169,19 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
@@ -17161,19 +17192,19 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
@@ -17184,19 +17215,19 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
@@ -17207,7 +17238,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
@@ -17216,10 +17247,10 @@
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
@@ -17230,19 +17261,19 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
@@ -17253,19 +17284,19 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
@@ -17276,19 +17307,19 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
@@ -17299,19 +17330,19 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
@@ -17322,19 +17353,19 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
@@ -17345,19 +17376,19 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
@@ -17368,19 +17399,19 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
@@ -17391,19 +17422,19 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H26" s="2">
         <v>10.0</v>
@@ -17414,7 +17445,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>34</v>
@@ -17423,10 +17454,10 @@
         <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
@@ -17437,19 +17468,19 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
@@ -17460,19 +17491,19 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
@@ -17483,19 +17514,19 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
@@ -17506,19 +17537,19 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H31" s="2">
         <v>10.0</v>
@@ -17529,19 +17560,19 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H32" s="2">
         <v>10.0</v>
@@ -17552,19 +17583,19 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
@@ -17575,19 +17606,19 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H34" s="2">
         <v>10.0</v>
@@ -17598,19 +17629,19 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
@@ -17621,19 +17652,19 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
@@ -17644,7 +17675,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>43</v>
@@ -17653,10 +17684,10 @@
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
@@ -17667,19 +17698,19 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H38" s="2">
         <v>10.0</v>
@@ -17690,7 +17721,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>34</v>
@@ -17699,10 +17730,10 @@
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
@@ -17713,19 +17744,19 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H40" s="2">
         <v>10.0</v>
@@ -17736,19 +17767,19 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
@@ -17759,19 +17790,19 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
@@ -17782,19 +17813,19 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H43" s="2">
         <v>10.0</v>
@@ -17805,19 +17836,19 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
@@ -17828,19 +17859,19 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H45" s="2">
         <v>10.0</v>
@@ -17851,19 +17882,19 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
@@ -17874,19 +17905,19 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H47" s="2">
         <v>10.0</v>
@@ -17897,19 +17928,19 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H48" s="2">
         <v>10.0</v>
@@ -17920,19 +17951,19 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H49" s="2">
         <v>10.0</v>
@@ -17943,19 +17974,19 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H50" s="2">
         <v>10.0</v>
@@ -17966,19 +17997,19 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H51" s="2">
         <v>10.0</v>
@@ -17989,19 +18020,19 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H52" s="2">
         <v>10.0</v>
@@ -18012,19 +18043,19 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H53" s="2">
         <v>10.0</v>
@@ -18035,19 +18066,19 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H54" s="2">
         <v>10.0</v>
@@ -18058,19 +18089,19 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H55" s="2">
         <v>10.0</v>
@@ -18081,19 +18112,19 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H56" s="2">
         <v>10.0</v>
@@ -18104,19 +18135,19 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H57" s="2">
         <v>10.0</v>
@@ -18127,7 +18158,7 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>38</v>
@@ -18136,10 +18167,10 @@
         <v>10</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H58" s="2">
         <v>10.0</v>
@@ -18150,19 +18181,19 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H59" s="2">
         <v>10.0</v>
@@ -18173,19 +18204,19 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G60" s="9"/>
       <c r="H60" s="2">
@@ -18197,19 +18228,19 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H61" s="2">
         <v>10.0</v>
@@ -18220,19 +18251,19 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H62" s="2">
         <v>10.0</v>
@@ -18243,19 +18274,19 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H63" s="2">
         <v>10.0</v>
@@ -18266,19 +18297,19 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H64" s="2">
         <v>10.0</v>
@@ -18289,19 +18320,19 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H65" s="2">
         <v>10.0</v>
@@ -18312,19 +18343,19 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H66" s="2">
         <v>10.0</v>
@@ -18335,19 +18366,19 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H67" s="2">
         <v>10.0</v>
@@ -18358,19 +18389,19 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H68" s="2">
         <v>10.0</v>
@@ -18381,7 +18412,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>9</v>
@@ -18390,10 +18421,10 @@
         <v>10</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="H69" s="2">
         <v>10.0</v>
@@ -18404,7 +18435,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>30</v>
@@ -18413,10 +18444,10 @@
         <v>10</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H70" s="2">
         <v>10.0</v>
@@ -18427,19 +18458,19 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H71" s="2">
         <v>10.0</v>
@@ -18450,19 +18481,19 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H72" s="2">
         <v>10.0</v>
@@ -18473,19 +18504,19 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H73" s="2">
         <v>10.0</v>
@@ -18496,19 +18527,19 @@
         <v>73.0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H74" s="2">
         <v>10.0</v>
@@ -18519,19 +18550,19 @@
         <v>74.0</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H75" s="2">
         <v>10.0</v>
@@ -18595,22 +18626,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H2" s="1">
         <v>4.0</v>
@@ -18621,22 +18652,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -18647,22 +18678,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -18673,22 +18704,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -18699,22 +18730,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
@@ -18725,19 +18756,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H7" s="1">
         <v>4.0</v>
@@ -18748,22 +18779,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H8" s="1">
         <v>4.0</v>
@@ -18774,22 +18805,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H9" s="1">
         <v>4.0</v>
@@ -18800,22 +18831,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H10" s="1">
         <v>4.0</v>
@@ -18826,22 +18857,22 @@
         <v>12.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H11" s="2">
         <v>3.0</v>
@@ -18852,22 +18883,22 @@
         <v>31.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H12" s="2">
         <v>4.0</v>
@@ -18878,7 +18909,7 @@
         <v>78.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>49</v>
@@ -18887,13 +18918,13 @@
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -18904,22 +18935,22 @@
         <v>10.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H14" s="2">
         <v>9.0</v>
@@ -18930,22 +18961,22 @@
         <v>11.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H15" s="2">
         <v>6.0</v>
@@ -18956,22 +18987,22 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H16" s="2">
         <v>6.0</v>
@@ -18982,16 +19013,16 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>16</v>
@@ -19005,22 +19036,22 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H18" s="2">
         <v>6.0</v>
@@ -19031,22 +19062,22 @@
         <v>16.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -19057,22 +19088,22 @@
         <v>17.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -19083,22 +19114,22 @@
         <v>18.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -19109,22 +19140,22 @@
         <v>19.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -19135,22 +19166,22 @@
         <v>20.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H23" s="2">
         <v>6.0</v>
@@ -19161,16 +19192,16 @@
         <v>21.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>16</v>
@@ -19184,16 +19215,16 @@
         <v>22.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>16</v>
@@ -19207,16 +19238,16 @@
         <v>23.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>16</v>
@@ -19230,16 +19261,16 @@
         <v>24.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>16</v>
@@ -19253,22 +19284,22 @@
         <v>25.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -19279,16 +19310,16 @@
         <v>26.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>16</v>
@@ -19302,16 +19333,16 @@
         <v>27.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>16</v>
@@ -19325,16 +19356,16 @@
         <v>28.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>16</v>
@@ -19348,16 +19379,16 @@
         <v>29.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>16</v>
@@ -19371,22 +19402,22 @@
         <v>30.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -19397,16 +19428,16 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>16</v>
@@ -19420,7 +19451,7 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>43</v>
@@ -19429,7 +19460,7 @@
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>16</v>
@@ -19443,22 +19474,22 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -19469,16 +19500,16 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>16</v>
@@ -19492,16 +19523,16 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>16</v>
@@ -19515,16 +19546,16 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>16</v>
@@ -19538,16 +19569,16 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>16</v>
@@ -19561,16 +19592,16 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>16</v>
@@ -19584,16 +19615,16 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>16</v>
@@ -19607,16 +19638,16 @@
         <v>41.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>16</v>
@@ -19630,16 +19661,16 @@
         <v>42.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>16</v>
@@ -19653,7 +19684,7 @@
         <v>43.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>9</v>
@@ -19662,7 +19693,7 @@
         <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>16</v>
@@ -19676,16 +19707,16 @@
         <v>44.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>16</v>
@@ -19699,22 +19730,22 @@
         <v>45.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H47" s="2">
         <v>9.0</v>
@@ -19725,22 +19756,22 @@
         <v>46.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -19751,7 +19782,7 @@
         <v>47.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>38</v>
@@ -19760,13 +19791,13 @@
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H49" s="2">
         <v>6.0</v>
@@ -19777,22 +19808,22 @@
         <v>48.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -19803,22 +19834,22 @@
         <v>49.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H51" s="2">
         <v>9.0</v>
@@ -19829,22 +19860,22 @@
         <v>50.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H52" s="2">
         <v>9.0</v>
@@ -19855,16 +19886,16 @@
         <v>51.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>16</v>
@@ -19878,16 +19909,16 @@
         <v>52.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>16</v>
@@ -19901,16 +19932,16 @@
         <v>53.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>16</v>
@@ -19924,22 +19955,22 @@
         <v>54.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H56" s="2">
         <v>9.0</v>
@@ -19950,16 +19981,16 @@
         <v>55.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>16</v>
@@ -19973,22 +20004,22 @@
         <v>56.0</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H58" s="2">
         <v>9.0</v>
@@ -19999,22 +20030,22 @@
         <v>57.0</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H59" s="2">
         <v>9.0</v>
@@ -20025,22 +20056,22 @@
         <v>58.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H60" s="2">
         <v>9.0</v>
@@ -20051,22 +20082,22 @@
         <v>59.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H61" s="2">
         <v>9.0</v>
@@ -20077,22 +20108,22 @@
         <v>60.0</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H62" s="2">
         <v>9.0</v>
@@ -20103,22 +20134,22 @@
         <v>61.0</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H63" s="2">
         <v>9.0</v>
@@ -20129,22 +20160,22 @@
         <v>62.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H64" s="2">
         <v>9.0</v>
@@ -20155,22 +20186,22 @@
         <v>63.0</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H65" s="2">
         <v>9.0</v>
@@ -20181,22 +20212,22 @@
         <v>64.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H66" s="2">
         <v>9.0</v>
@@ -20207,22 +20238,22 @@
         <v>65.0</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H67" s="2">
         <v>9.0</v>
@@ -20233,22 +20264,22 @@
         <v>66.0</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H68" s="2">
         <v>9.0</v>
@@ -20259,22 +20290,22 @@
         <v>67.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H69" s="2">
         <v>9.0</v>
@@ -20285,7 +20316,7 @@
         <v>68.0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>34</v>
@@ -20294,13 +20325,13 @@
         <v>10</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H70" s="2">
         <v>6.0</v>
@@ -20311,22 +20342,22 @@
         <v>69.0</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H71" s="2">
         <v>6.0</v>
@@ -20337,22 +20368,22 @@
         <v>70.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H72" s="2">
         <v>9.0</v>
@@ -20363,22 +20394,22 @@
         <v>71.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H73" s="2">
         <v>9.0</v>
@@ -20389,16 +20420,16 @@
         <v>72.0</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>16</v>
@@ -20412,16 +20443,16 @@
         <v>73.0</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>16</v>
@@ -20435,22 +20466,22 @@
         <v>74.0</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H76" s="2">
         <v>6.0</v>
@@ -20461,16 +20492,16 @@
         <v>75.0</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>16</v>
@@ -20484,7 +20515,7 @@
         <v>76.0</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>19</v>
@@ -20493,7 +20524,7 @@
         <v>10</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>16</v>
@@ -20507,16 +20538,16 @@
         <v>77.0</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>16</v>
@@ -20530,22 +20561,22 @@
         <v>78.0</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H80" s="2">
         <v>9.0</v>
@@ -20556,22 +20587,22 @@
         <v>79.0</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H81" s="2">
         <v>9.0</v>
@@ -20582,22 +20613,22 @@
         <v>80.0</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H82" s="2">
         <v>9.0</v>
@@ -20608,22 +20639,22 @@
         <v>81.0</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H83" s="2">
         <v>9.0</v>
@@ -20634,22 +20665,22 @@
         <v>82.0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H84" s="2">
         <v>4.0</v>
@@ -20660,22 +20691,22 @@
         <v>83.0</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H85" s="2">
         <v>9.0</v>
@@ -20686,22 +20717,22 @@
         <v>84.0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H86" s="2">
         <v>9.0</v>
@@ -20712,22 +20743,22 @@
         <v>85.0</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H87" s="2">
         <v>9.0</v>
@@ -20738,22 +20769,22 @@
         <v>86.0</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H88" s="2">
         <v>9.0</v>
@@ -20764,22 +20795,22 @@
         <v>87.0</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H89" s="2">
         <v>9.0</v>
@@ -20790,7 +20821,7 @@
         <v>88.0</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>19</v>
@@ -20799,13 +20830,13 @@
         <v>10</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H90" s="2">
         <v>9.0</v>
@@ -20816,16 +20847,16 @@
         <v>89.0</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>16</v>
@@ -21805,22 +21836,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -21831,22 +21862,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -21857,22 +21888,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -21883,22 +21914,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -21909,22 +21940,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
@@ -21935,22 +21966,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H7" s="2">
         <v>4.0</v>
@@ -21961,22 +21992,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -21987,22 +22018,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -22013,22 +22044,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H10" s="1">
         <v>5.0</v>
@@ -22039,22 +22070,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -22065,22 +22096,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -22091,22 +22122,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -22117,22 +22148,22 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H14" s="2">
         <v>6.0</v>
@@ -22143,22 +22174,22 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -22169,22 +22200,22 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -22195,22 +22226,22 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H17" s="2">
         <v>6.0</v>
@@ -22221,22 +22252,22 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -22247,22 +22278,22 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H19" s="1">
         <v>6.0</v>
@@ -22273,19 +22304,19 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -22296,22 +22327,22 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -22322,22 +22353,22 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -22348,7 +22379,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>30</v>
@@ -22357,13 +22388,13 @@
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -22374,22 +22405,22 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -22400,22 +22431,22 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -22426,22 +22457,22 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="H26" s="2">
         <v>3.0</v>
@@ -22452,22 +22483,22 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -22478,22 +22509,22 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -22504,22 +22535,22 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H29" s="2">
         <v>9.0</v>
@@ -22530,22 +22561,22 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H30" s="2">
         <v>9.0</v>
@@ -22556,22 +22587,22 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H31" s="2">
         <v>9.0</v>
@@ -22582,22 +22613,22 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H32" s="2">
         <v>9.0</v>
@@ -22608,22 +22639,22 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -22634,7 +22665,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>43</v>
@@ -22643,13 +22674,13 @@
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H34" s="2">
         <v>9.0</v>
@@ -22660,22 +22691,22 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="H35" s="2">
         <v>9.0</v>
@@ -22686,22 +22717,22 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -22712,22 +22743,22 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H37" s="2">
         <v>9.0</v>
@@ -22738,19 +22769,19 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="H38" s="2">
         <v>9.0</v>
@@ -22761,22 +22792,22 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="H39" s="2">
         <v>9.0</v>
@@ -22787,22 +22818,22 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H40" s="2">
         <v>9.0</v>
@@ -22813,22 +22844,22 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H41" s="2">
         <v>9.0</v>
@@ -22839,22 +22870,22 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H42" s="2">
         <v>9.0</v>
@@ -22865,7 +22896,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>27</v>
@@ -22874,13 +22905,13 @@
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="H43" s="2">
         <v>9.0</v>
@@ -22891,19 +22922,19 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H44" s="2">
         <v>9.0</v>
@@ -22914,19 +22945,19 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H45" s="2">
         <v>6.0</v>
@@ -22937,19 +22968,19 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H46" s="2">
         <v>9.0</v>
@@ -22960,19 +22991,19 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H47" s="2">
         <v>6.0</v>
@@ -22983,22 +23014,22 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -23009,22 +23040,22 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="H49" s="2">
         <v>9.0</v>
@@ -23035,22 +23066,22 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -24066,22 +24097,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -24092,22 +24123,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -24118,22 +24149,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -24144,22 +24175,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -24170,22 +24201,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -24196,22 +24227,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -24222,22 +24253,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="H8" s="2">
         <v>4.0</v>
@@ -24248,22 +24279,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H9" s="2">
         <v>6.0</v>
@@ -24274,22 +24305,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -24300,22 +24331,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -24326,22 +24357,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H12" s="2">
         <v>5.0</v>
@@ -24352,22 +24383,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H13" s="2">
         <v>3.0</v>
@@ -24378,19 +24409,19 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H14" s="1">
         <v>6.0</v>
@@ -24401,22 +24432,22 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -24427,22 +24458,22 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -24453,22 +24484,22 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="H17" s="2">
         <v>9.0</v>
@@ -24479,22 +24510,22 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -24505,22 +24536,22 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -24531,22 +24562,22 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H20" s="2">
         <v>7.0</v>
@@ -24557,22 +24588,22 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H21" s="2">
         <v>7.0</v>
@@ -24583,22 +24614,22 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -24609,19 +24640,19 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -24632,22 +24663,22 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -24658,22 +24689,22 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -24684,22 +24715,22 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H26" s="2">
         <v>9.0</v>
@@ -24710,22 +24741,22 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -25764,7 +25795,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
@@ -25773,13 +25804,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -25790,22 +25821,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H3" s="2">
         <v>7.0</v>
@@ -25816,22 +25847,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -25842,22 +25873,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -25868,22 +25899,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -25894,22 +25925,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -25920,19 +25951,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H8" s="2">
         <v>6.0</v>
@@ -25943,22 +25974,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -25969,19 +26000,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H10" s="2">
         <v>6.0</v>
@@ -27033,22 +27064,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="H2" s="2">
         <v>2.0</v>
@@ -27059,22 +27090,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -27085,22 +27116,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -27111,22 +27142,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H5" s="1">
         <v>5.0</v>
@@ -27137,22 +27168,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -27163,22 +27194,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>
@@ -27189,19 +27220,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -27212,22 +27243,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -27238,19 +27269,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -27261,22 +27292,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -27287,22 +27318,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -27313,22 +27344,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="H13" s="2">
         <v>9.0</v>
@@ -28376,22 +28407,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -28402,22 +28433,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -28428,22 +28459,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -28454,19 +28485,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H5" s="2">
         <v>9.0</v>
@@ -28477,22 +28508,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -28503,22 +28534,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -28529,22 +28560,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="H8" s="2">
         <v>5.0</v>
@@ -29598,22 +29629,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -29624,22 +29655,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -29650,19 +29681,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -29673,22 +29704,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -29699,22 +29730,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H6" s="2">
         <v>7.0</v>
@@ -29725,22 +29756,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="895">
   <si>
     <t>id</t>
   </si>
@@ -193,6 +193,18 @@
   </si>
   <si>
     <t>./public/member-images/2026/DUONG_THI_MINH_TRANG.webp</t>
+  </si>
+  <si>
+    <t>Nguyễn Thái Bảo</t>
+  </si>
+  <si>
+    <t>Bảo</t>
+  </si>
+  <si>
+    <t>Bảo Kỹ Thuật</t>
+  </si>
+  <si>
+    <t>./public/member-images/2026/NGUYEN_THAI_BAO.webp</t>
   </si>
   <si>
     <t>Lê Thị Thuỳ Trang</t>
@@ -3420,7 +3432,32 @@
         <v>6.0</v>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
     <row r="15" ht="15.75" customHeight="1"/>
     <row r="16" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
@@ -4463,22 +4500,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -4489,22 +4526,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="H3" s="2">
         <v>2.0</v>
@@ -4515,22 +4552,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="H4" s="2">
         <v>6.0</v>
@@ -4541,22 +4578,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="H5" s="1">
         <v>3.0</v>
@@ -4567,22 +4604,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -4593,22 +4630,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="H7" s="1">
         <v>6.0</v>
@@ -4619,22 +4656,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -4645,22 +4682,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -5710,22 +5747,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6780,22 +6817,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6806,22 +6843,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -7875,22 +7912,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="H2" s="7">
         <v>5.0</v>
@@ -8945,19 +8982,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -8968,19 +9005,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -10037,22 +10074,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -10063,22 +10100,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -10089,22 +10126,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="H4" s="2">
         <v>4.0</v>
@@ -10115,22 +10152,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -11184,22 +11221,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -11210,22 +11247,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -11236,22 +11273,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -11262,22 +11299,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="H5" s="1">
         <v>6.0</v>
@@ -11288,22 +11325,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="H6" s="2">
         <v>6.0</v>
@@ -12326,7 +12363,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -15489,7 +15526,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>49</v>
@@ -15498,13 +15535,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -15515,22 +15552,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -15541,7 +15578,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>34</v>
@@ -15550,13 +15587,13 @@
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -15567,22 +15604,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H5" s="2">
         <v>9.0</v>
@@ -15593,22 +15630,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -15619,7 +15656,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>19</v>
@@ -15628,13 +15665,13 @@
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -15645,22 +15682,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -15671,22 +15708,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -15706,13 +15743,13 @@
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H10" s="2">
         <v>6.0</v>
@@ -15723,22 +15760,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -15749,16 +15786,16 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>16</v>
@@ -15772,22 +15809,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -15798,22 +15835,22 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2">
         <v>9.0</v>
@@ -16855,22 +16892,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="H2" s="2">
         <v>8.0</v>
@@ -16881,19 +16918,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>787</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H3" s="2">
         <v>8.0</v>
@@ -16904,22 +16941,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="H4" s="2">
         <v>8.0</v>
@@ -16930,19 +16967,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H5" s="2">
         <v>8.0</v>
@@ -16953,19 +16990,19 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H6" s="2">
         <v>8.0</v>
@@ -16976,22 +17013,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="H7" s="2">
         <v>5.0</v>
@@ -17002,22 +17039,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -17028,22 +17065,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -17054,19 +17091,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H10" s="2">
         <v>7.0</v>
@@ -17077,19 +17114,19 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -17100,19 +17137,19 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H12" s="2">
         <v>10.0</v>
@@ -17123,19 +17160,19 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
@@ -17146,19 +17183,19 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
@@ -17169,19 +17206,19 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
@@ -17192,19 +17229,19 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
@@ -17215,19 +17252,19 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
@@ -17238,7 +17275,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
@@ -17247,10 +17284,10 @@
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
@@ -17261,19 +17298,19 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
@@ -17284,19 +17321,19 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
@@ -17307,19 +17344,19 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
@@ -17330,19 +17367,19 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
@@ -17353,19 +17390,19 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
@@ -17376,19 +17413,19 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
@@ -17399,19 +17436,19 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
@@ -17422,19 +17459,19 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H26" s="2">
         <v>10.0</v>
@@ -17445,7 +17482,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>34</v>
@@ -17454,10 +17491,10 @@
         <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
@@ -17468,19 +17505,19 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
@@ -17491,19 +17528,19 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
@@ -17514,19 +17551,19 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
@@ -17537,19 +17574,19 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H31" s="2">
         <v>10.0</v>
@@ -17560,19 +17597,19 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H32" s="2">
         <v>10.0</v>
@@ -17583,19 +17620,19 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
@@ -17606,19 +17643,19 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H34" s="2">
         <v>10.0</v>
@@ -17629,19 +17666,19 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
@@ -17652,19 +17689,19 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
@@ -17675,7 +17712,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>43</v>
@@ -17684,10 +17721,10 @@
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
@@ -17698,19 +17735,19 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H38" s="2">
         <v>10.0</v>
@@ -17721,7 +17758,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>34</v>
@@ -17730,10 +17767,10 @@
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
@@ -17744,19 +17781,19 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H40" s="2">
         <v>10.0</v>
@@ -17767,19 +17804,19 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
@@ -17790,19 +17827,19 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
@@ -17813,19 +17850,19 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H43" s="2">
         <v>10.0</v>
@@ -17836,19 +17873,19 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
@@ -17859,19 +17896,19 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H45" s="2">
         <v>10.0</v>
@@ -17882,19 +17919,19 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
@@ -17905,19 +17942,19 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H47" s="2">
         <v>10.0</v>
@@ -17928,19 +17965,19 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H48" s="2">
         <v>10.0</v>
@@ -17951,19 +17988,19 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H49" s="2">
         <v>10.0</v>
@@ -17974,19 +18011,19 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H50" s="2">
         <v>10.0</v>
@@ -17997,19 +18034,19 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H51" s="2">
         <v>10.0</v>
@@ -18020,19 +18057,19 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H52" s="2">
         <v>10.0</v>
@@ -18043,19 +18080,19 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H53" s="2">
         <v>10.0</v>
@@ -18066,19 +18103,19 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H54" s="2">
         <v>10.0</v>
@@ -18089,19 +18126,19 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H55" s="2">
         <v>10.0</v>
@@ -18112,19 +18149,19 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H56" s="2">
         <v>10.0</v>
@@ -18135,19 +18172,19 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H57" s="2">
         <v>10.0</v>
@@ -18158,7 +18195,7 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>38</v>
@@ -18167,10 +18204,10 @@
         <v>10</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H58" s="2">
         <v>10.0</v>
@@ -18181,19 +18218,19 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H59" s="2">
         <v>10.0</v>
@@ -18204,19 +18241,19 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G60" s="9"/>
       <c r="H60" s="2">
@@ -18228,19 +18265,19 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H61" s="2">
         <v>10.0</v>
@@ -18251,19 +18288,19 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H62" s="2">
         <v>10.0</v>
@@ -18274,19 +18311,19 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H63" s="2">
         <v>10.0</v>
@@ -18297,19 +18334,19 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H64" s="2">
         <v>10.0</v>
@@ -18320,19 +18357,19 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H65" s="2">
         <v>10.0</v>
@@ -18343,19 +18380,19 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H66" s="2">
         <v>10.0</v>
@@ -18366,19 +18403,19 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H67" s="2">
         <v>10.0</v>
@@ -18389,19 +18426,19 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H68" s="2">
         <v>10.0</v>
@@ -18412,7 +18449,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>9</v>
@@ -18421,10 +18458,10 @@
         <v>10</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="H69" s="2">
         <v>10.0</v>
@@ -18435,7 +18472,7 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>30</v>
@@ -18444,10 +18481,10 @@
         <v>10</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H70" s="2">
         <v>10.0</v>
@@ -18458,19 +18495,19 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H71" s="2">
         <v>10.0</v>
@@ -18481,19 +18518,19 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H72" s="2">
         <v>10.0</v>
@@ -18504,19 +18541,19 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H73" s="2">
         <v>10.0</v>
@@ -18527,19 +18564,19 @@
         <v>73.0</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H74" s="2">
         <v>10.0</v>
@@ -18550,19 +18587,19 @@
         <v>74.0</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H75" s="2">
         <v>10.0</v>
@@ -18626,22 +18663,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H2" s="1">
         <v>4.0</v>
@@ -18652,22 +18689,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -18678,22 +18715,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -18704,22 +18741,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -18730,22 +18767,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
@@ -18756,19 +18793,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H7" s="1">
         <v>4.0</v>
@@ -18779,22 +18816,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H8" s="1">
         <v>4.0</v>
@@ -18805,22 +18842,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H9" s="1">
         <v>4.0</v>
@@ -18831,22 +18868,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H10" s="1">
         <v>4.0</v>
@@ -18857,22 +18894,22 @@
         <v>12.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H11" s="2">
         <v>3.0</v>
@@ -18883,22 +18920,22 @@
         <v>31.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H12" s="2">
         <v>4.0</v>
@@ -18909,7 +18946,7 @@
         <v>78.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>49</v>
@@ -18918,13 +18955,13 @@
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -18935,22 +18972,22 @@
         <v>10.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H14" s="2">
         <v>9.0</v>
@@ -18961,22 +18998,22 @@
         <v>11.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H15" s="2">
         <v>6.0</v>
@@ -18987,22 +19024,22 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H16" s="2">
         <v>6.0</v>
@@ -19013,16 +19050,16 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>16</v>
@@ -19036,22 +19073,22 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H18" s="2">
         <v>6.0</v>
@@ -19062,22 +19099,22 @@
         <v>16.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -19088,22 +19125,22 @@
         <v>17.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -19114,22 +19151,22 @@
         <v>18.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -19140,22 +19177,22 @@
         <v>19.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -19166,22 +19203,22 @@
         <v>20.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H23" s="2">
         <v>6.0</v>
@@ -19192,16 +19229,16 @@
         <v>21.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>16</v>
@@ -19215,16 +19252,16 @@
         <v>22.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>16</v>
@@ -19238,16 +19275,16 @@
         <v>23.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>16</v>
@@ -19261,16 +19298,16 @@
         <v>24.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>16</v>
@@ -19284,22 +19321,22 @@
         <v>25.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -19310,16 +19347,16 @@
         <v>26.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>16</v>
@@ -19333,16 +19370,16 @@
         <v>27.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>16</v>
@@ -19356,16 +19393,16 @@
         <v>28.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>16</v>
@@ -19379,16 +19416,16 @@
         <v>29.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>16</v>
@@ -19402,22 +19439,22 @@
         <v>30.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -19428,16 +19465,16 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>16</v>
@@ -19451,7 +19488,7 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>43</v>
@@ -19460,7 +19497,7 @@
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>16</v>
@@ -19474,22 +19511,22 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -19500,16 +19537,16 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>16</v>
@@ -19523,16 +19560,16 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>16</v>
@@ -19546,16 +19583,16 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>16</v>
@@ -19569,16 +19606,16 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>16</v>
@@ -19592,16 +19629,16 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>16</v>
@@ -19615,16 +19652,16 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>16</v>
@@ -19638,16 +19675,16 @@
         <v>41.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>16</v>
@@ -19661,16 +19698,16 @@
         <v>42.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>16</v>
@@ -19684,7 +19721,7 @@
         <v>43.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>9</v>
@@ -19693,7 +19730,7 @@
         <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>16</v>
@@ -19707,16 +19744,16 @@
         <v>44.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>16</v>
@@ -19730,22 +19767,22 @@
         <v>45.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H47" s="2">
         <v>9.0</v>
@@ -19756,22 +19793,22 @@
         <v>46.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -19782,7 +19819,7 @@
         <v>47.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>38</v>
@@ -19791,13 +19828,13 @@
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H49" s="2">
         <v>6.0</v>
@@ -19808,22 +19845,22 @@
         <v>48.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -19834,22 +19871,22 @@
         <v>49.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H51" s="2">
         <v>9.0</v>
@@ -19860,22 +19897,22 @@
         <v>50.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H52" s="2">
         <v>9.0</v>
@@ -19886,16 +19923,16 @@
         <v>51.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>16</v>
@@ -19909,16 +19946,16 @@
         <v>52.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>16</v>
@@ -19932,16 +19969,16 @@
         <v>53.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>16</v>
@@ -19955,22 +19992,22 @@
         <v>54.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H56" s="2">
         <v>9.0</v>
@@ -19981,16 +20018,16 @@
         <v>55.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>16</v>
@@ -20004,22 +20041,22 @@
         <v>56.0</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="H58" s="2">
         <v>9.0</v>
@@ -20030,22 +20067,22 @@
         <v>57.0</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H59" s="2">
         <v>9.0</v>
@@ -20056,22 +20093,22 @@
         <v>58.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H60" s="2">
         <v>9.0</v>
@@ -20082,22 +20119,22 @@
         <v>59.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H61" s="2">
         <v>9.0</v>
@@ -20108,22 +20145,22 @@
         <v>60.0</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H62" s="2">
         <v>9.0</v>
@@ -20134,22 +20171,22 @@
         <v>61.0</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H63" s="2">
         <v>9.0</v>
@@ -20160,22 +20197,22 @@
         <v>62.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="H64" s="2">
         <v>9.0</v>
@@ -20186,22 +20223,22 @@
         <v>63.0</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="H65" s="2">
         <v>9.0</v>
@@ -20212,22 +20249,22 @@
         <v>64.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="H66" s="2">
         <v>9.0</v>
@@ -20238,22 +20275,22 @@
         <v>65.0</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="H67" s="2">
         <v>9.0</v>
@@ -20264,22 +20301,22 @@
         <v>66.0</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H68" s="2">
         <v>9.0</v>
@@ -20290,22 +20327,22 @@
         <v>67.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H69" s="2">
         <v>9.0</v>
@@ -20316,7 +20353,7 @@
         <v>68.0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>34</v>
@@ -20325,13 +20362,13 @@
         <v>10</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="H70" s="2">
         <v>6.0</v>
@@ -20342,22 +20379,22 @@
         <v>69.0</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H71" s="2">
         <v>6.0</v>
@@ -20368,22 +20405,22 @@
         <v>70.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="H72" s="2">
         <v>9.0</v>
@@ -20394,22 +20431,22 @@
         <v>71.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="H73" s="2">
         <v>9.0</v>
@@ -20420,16 +20457,16 @@
         <v>72.0</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>16</v>
@@ -20443,16 +20480,16 @@
         <v>73.0</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>16</v>
@@ -20466,22 +20503,22 @@
         <v>74.0</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H76" s="2">
         <v>6.0</v>
@@ -20492,16 +20529,16 @@
         <v>75.0</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>16</v>
@@ -20515,7 +20552,7 @@
         <v>76.0</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>19</v>
@@ -20524,7 +20561,7 @@
         <v>10</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>16</v>
@@ -20538,16 +20575,16 @@
         <v>77.0</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>16</v>
@@ -20561,22 +20598,22 @@
         <v>78.0</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H80" s="2">
         <v>9.0</v>
@@ -20587,22 +20624,22 @@
         <v>79.0</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H81" s="2">
         <v>9.0</v>
@@ -20613,22 +20650,22 @@
         <v>80.0</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H82" s="2">
         <v>9.0</v>
@@ -20639,22 +20676,22 @@
         <v>81.0</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H83" s="2">
         <v>9.0</v>
@@ -20665,22 +20702,22 @@
         <v>82.0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="H84" s="2">
         <v>4.0</v>
@@ -20691,22 +20728,22 @@
         <v>83.0</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="H85" s="2">
         <v>9.0</v>
@@ -20717,22 +20754,22 @@
         <v>84.0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="H86" s="2">
         <v>9.0</v>
@@ -20743,22 +20780,22 @@
         <v>85.0</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H87" s="2">
         <v>9.0</v>
@@ -20769,22 +20806,22 @@
         <v>86.0</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="H88" s="2">
         <v>9.0</v>
@@ -20795,22 +20832,22 @@
         <v>87.0</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H89" s="2">
         <v>9.0</v>
@@ -20821,7 +20858,7 @@
         <v>88.0</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>19</v>
@@ -20830,13 +20867,13 @@
         <v>10</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="H90" s="2">
         <v>9.0</v>
@@ -20847,16 +20884,16 @@
         <v>89.0</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>16</v>
@@ -21836,22 +21873,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -21862,22 +21899,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -21888,22 +21925,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -21914,22 +21951,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -21940,22 +21977,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
@@ -21966,22 +22003,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H7" s="2">
         <v>4.0</v>
@@ -21992,22 +22029,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -22018,22 +22055,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -22044,22 +22081,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H10" s="1">
         <v>5.0</v>
@@ -22070,22 +22107,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -22096,22 +22133,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -22122,22 +22159,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -22148,22 +22185,22 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="H14" s="2">
         <v>6.0</v>
@@ -22174,22 +22211,22 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -22200,22 +22237,22 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -22226,22 +22263,22 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H17" s="2">
         <v>6.0</v>
@@ -22252,22 +22289,22 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -22278,22 +22315,22 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="H19" s="1">
         <v>6.0</v>
@@ -22304,19 +22341,19 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -22327,22 +22364,22 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -22353,22 +22390,22 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -22379,7 +22416,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>30</v>
@@ -22388,13 +22425,13 @@
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -22405,22 +22442,22 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -22431,22 +22468,22 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -22457,22 +22494,22 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="H26" s="2">
         <v>3.0</v>
@@ -22483,22 +22520,22 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -22509,22 +22546,22 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -22535,22 +22572,22 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="H29" s="2">
         <v>9.0</v>
@@ -22561,22 +22598,22 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="H30" s="2">
         <v>9.0</v>
@@ -22587,22 +22624,22 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H31" s="2">
         <v>9.0</v>
@@ -22613,22 +22650,22 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="H32" s="2">
         <v>9.0</v>
@@ -22639,22 +22676,22 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -22665,7 +22702,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>43</v>
@@ -22674,13 +22711,13 @@
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="H34" s="2">
         <v>9.0</v>
@@ -22691,22 +22728,22 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H35" s="2">
         <v>9.0</v>
@@ -22717,22 +22754,22 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -22743,22 +22780,22 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="H37" s="2">
         <v>9.0</v>
@@ -22769,19 +22806,19 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H38" s="2">
         <v>9.0</v>
@@ -22792,22 +22829,22 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="H39" s="2">
         <v>9.0</v>
@@ -22818,22 +22855,22 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="H40" s="2">
         <v>9.0</v>
@@ -22844,22 +22881,22 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="H41" s="2">
         <v>9.0</v>
@@ -22870,22 +22907,22 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="H42" s="2">
         <v>9.0</v>
@@ -22896,7 +22933,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>27</v>
@@ -22905,13 +22942,13 @@
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="H43" s="2">
         <v>9.0</v>
@@ -22922,19 +22959,19 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H44" s="2">
         <v>9.0</v>
@@ -22945,19 +22982,19 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="H45" s="2">
         <v>6.0</v>
@@ -22968,19 +23005,19 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H46" s="2">
         <v>9.0</v>
@@ -22991,19 +23028,19 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="H47" s="2">
         <v>6.0</v>
@@ -23014,22 +23051,22 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -23040,22 +23077,22 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H49" s="2">
         <v>9.0</v>
@@ -23066,22 +23103,22 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -24097,22 +24134,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -24123,22 +24160,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -24149,22 +24186,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -24175,22 +24212,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -24201,22 +24238,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -24227,22 +24264,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -24253,22 +24290,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="H8" s="2">
         <v>4.0</v>
@@ -24279,22 +24316,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="H9" s="2">
         <v>6.0</v>
@@ -24305,22 +24342,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -24331,22 +24368,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -24357,22 +24394,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="H12" s="2">
         <v>5.0</v>
@@ -24383,22 +24420,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="H13" s="2">
         <v>3.0</v>
@@ -24409,19 +24446,19 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H14" s="1">
         <v>6.0</v>
@@ -24432,22 +24469,22 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -24458,22 +24495,22 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -24484,22 +24521,22 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="H17" s="2">
         <v>9.0</v>
@@ -24510,22 +24547,22 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -24536,22 +24573,22 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -24562,22 +24599,22 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="H20" s="2">
         <v>7.0</v>
@@ -24588,22 +24625,22 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="H21" s="2">
         <v>7.0</v>
@@ -24614,22 +24651,22 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -24640,19 +24677,19 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -24663,22 +24700,22 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -24689,22 +24726,22 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -24715,22 +24752,22 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="H26" s="2">
         <v>9.0</v>
@@ -24741,22 +24778,22 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -25795,7 +25832,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
@@ -25804,13 +25841,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -25821,22 +25858,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="H3" s="2">
         <v>7.0</v>
@@ -25847,22 +25884,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -25873,22 +25910,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -25899,22 +25936,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -25925,22 +25962,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -25951,19 +25988,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H8" s="2">
         <v>6.0</v>
@@ -25974,22 +26011,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -26000,19 +26037,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H10" s="2">
         <v>6.0</v>
@@ -27064,22 +27101,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="H2" s="2">
         <v>2.0</v>
@@ -27090,22 +27127,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -27116,22 +27153,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -27142,22 +27179,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="H5" s="1">
         <v>5.0</v>
@@ -27168,22 +27205,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -27194,22 +27231,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>
@@ -27220,19 +27257,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -27243,22 +27280,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -27269,19 +27306,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -27292,22 +27329,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -27318,22 +27355,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -27344,22 +27381,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="H13" s="2">
         <v>9.0</v>
@@ -28407,22 +28444,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -28433,22 +28470,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -28459,22 +28496,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -28485,19 +28522,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H5" s="2">
         <v>9.0</v>
@@ -28508,22 +28545,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -28534,22 +28571,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -28560,22 +28597,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="H8" s="2">
         <v>5.0</v>
@@ -29629,22 +29666,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -29655,22 +29692,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -29681,19 +29718,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -29704,22 +29741,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -29730,22 +29767,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="H6" s="2">
         <v>7.0</v>
@@ -29756,22 +29793,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="894">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="899">
   <si>
     <t>id</t>
   </si>
@@ -97,22 +97,25 @@
     <t>./public/member-images/2026/TRAN_THI_ANH_THU.webp</t>
   </si>
   <si>
-    <t>Lê Thị Mận (Mân)</t>
+    <t>Lê Thị Mận (mân mân)</t>
   </si>
   <si>
     <t>Mận</t>
   </si>
   <si>
-    <t>Lê Mân</t>
+    <t>má hồng iu đời 🙈</t>
   </si>
   <si>
     <t>./public/member-images/2026/LE_THI_MAN.webp</t>
   </si>
   <si>
-    <t>Hồ Mỹ Lâm Uyên</t>
+    <t>Hồ Mỹ Lâm Uyên (Min)</t>
   </si>
   <si>
     <t>Uyên</t>
+  </si>
+  <si>
+    <t>A little soft, a little dreamy, a lot of love 🩷</t>
   </si>
   <si>
     <t>./public/member-images/2026/HO_MY_LAM_UYEN.webp</t>
@@ -1049,9 +1052,6 @@
     <t>Đặng Hoàng Hoài Thư</t>
   </si>
   <si>
-    <t>Thực tập Ban chấp hành</t>
-  </si>
-  <si>
     <t>./public/member-images/2024/DANG_HOANG_HOAI_THU.webp</t>
   </si>
   <si>
@@ -1553,7 +1553,13 @@
     <t>Trung Bảo</t>
   </si>
   <si>
-    <t>Hoàng Trần Bảo Anh</t>
+    <t>./public/member-images/2023/VO_NU_HUYEN_TRAN.webp</t>
+  </si>
+  <si>
+    <t>Hoàng Trần Bảo Anh (Tea)</t>
+  </si>
+  <si>
+    <t>./public/member-images/2023/HOANG_TRAN_BAO_ANH.webp</t>
   </si>
   <si>
     <t>Huỳnh Công Nhật Quang</t>
@@ -2728,6 +2734,15 @@
   </si>
   <si>
     <t>Bùi Thị Mỹ Vân</t>
+  </si>
+  <si>
+    <t>Thân An Tường Nhi</t>
+  </si>
+  <si>
+    <t>Vân Du</t>
+  </si>
+  <si>
+    <t>./public/member-images/NO/THAN_AN_TUONG_NHI.webp</t>
   </si>
 </sst>
 </file>
@@ -2775,7 +2790,7 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+      <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -3213,10 +3228,10 @@
         <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H5" s="2">
         <v>6.0</v>
@@ -3227,22 +3242,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" s="2">
         <v>6.0</v>
@@ -3253,22 +3268,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -3279,22 +3294,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H8" s="2">
         <v>6.0</v>
@@ -3305,22 +3320,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2">
         <v>6.0</v>
@@ -3331,22 +3346,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H10" s="2">
         <v>6.0</v>
@@ -3357,7 +3372,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>23</v>
@@ -3366,13 +3381,13 @@
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -3383,22 +3398,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H12" s="2">
         <v>6.0</v>
@@ -3409,22 +3424,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -3435,10 +3450,10 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -3450,7 +3465,7 @@
         <v>12</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14" s="2">
         <v>6.0</v>
@@ -4503,22 +4518,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -4529,22 +4544,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="H3" s="2">
         <v>2.0</v>
@@ -4555,7 +4570,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>402</v>
@@ -4567,10 +4582,10 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="H4" s="2">
         <v>6.0</v>
@@ -4581,22 +4596,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="H5" s="1">
         <v>3.0</v>
@@ -4607,22 +4622,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -4633,10 +4648,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -4645,10 +4660,10 @@
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="H7" s="1">
         <v>6.0</v>
@@ -4659,22 +4674,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -4685,22 +4700,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -4711,16 +4726,16 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>449</v>
@@ -5772,22 +5787,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6842,22 +6857,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6868,22 +6883,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -7932,27 +7947,27 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="23.25" customHeight="1">
       <c r="A2" s="7">
         <v>1.0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>419</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="H2" s="7">
         <v>5.0</v>
@@ -9007,19 +9022,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -9030,16 +9045,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>449</v>
@@ -10099,22 +10114,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -10125,22 +10140,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -10151,22 +10166,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="H4" s="2">
         <v>4.0</v>
@@ -10177,22 +10192,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -11246,22 +11261,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -11272,22 +11287,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -11298,22 +11313,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>483</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -11324,10 +11339,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -11336,10 +11351,10 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="H5" s="1">
         <v>6.0</v>
@@ -11350,22 +11365,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="H6" s="2">
         <v>6.0</v>
@@ -12388,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -14500,22 +14515,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="H2" s="2">
         <v>8.0</v>
@@ -14526,16 +14541,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>449</v>
@@ -14549,22 +14564,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>449</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="H4" s="2">
         <v>8.0</v>
@@ -14575,16 +14590,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>449</v>
@@ -14598,16 +14613,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>449</v>
@@ -15667,22 +15682,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -15693,22 +15708,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -15719,22 +15734,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -15745,10 +15760,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -15757,10 +15772,10 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H5" s="2">
         <v>9.0</v>
@@ -15771,22 +15786,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -15797,22 +15812,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -15823,22 +15838,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -15849,22 +15864,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -15884,13 +15899,13 @@
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H10" s="2">
         <v>6.0</v>
@@ -15901,10 +15916,10 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
@@ -15913,10 +15928,10 @@
         <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -15927,16 +15942,16 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>12</v>
@@ -15950,10 +15965,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -15962,10 +15977,10 @@
         <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -15976,22 +15991,22 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2">
         <v>9.0</v>
@@ -16998,7 +17013,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
+    <col customWidth="1" min="1" max="1" width="5.11"/>
     <col customWidth="1" min="2" max="2" width="22.44"/>
+    <col customWidth="1" min="5" max="5" width="13.89"/>
     <col customWidth="1" min="7" max="7" width="29.22"/>
   </cols>
   <sheetData>
@@ -17033,22 +17050,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -17059,13 +17076,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -17074,7 +17091,7 @@
         <v>449</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="H3" s="2">
         <v>7.0</v>
@@ -17085,13 +17102,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>11</v>
@@ -17100,7 +17117,7 @@
         <v>449</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -17111,16 +17128,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>449</v>
@@ -17134,16 +17151,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>449</v>
@@ -17157,16 +17174,16 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>449</v>
@@ -17180,10 +17197,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -17192,7 +17209,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
@@ -17203,16 +17220,16 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>449</v>
@@ -17226,16 +17243,16 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>449</v>
@@ -17249,7 +17266,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>23</v>
@@ -17258,7 +17275,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>449</v>
@@ -17272,7 +17289,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>363</v>
@@ -17281,7 +17298,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>449</v>
@@ -17295,16 +17312,16 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>449</v>
@@ -17318,16 +17335,16 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>449</v>
@@ -17341,16 +17358,16 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>449</v>
@@ -17364,16 +17381,16 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>449</v>
@@ -17387,16 +17404,16 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>449</v>
@@ -17410,16 +17427,16 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>449</v>
@@ -17433,16 +17450,16 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>449</v>
@@ -17456,16 +17473,16 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>449</v>
@@ -17479,16 +17496,16 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>449</v>
@@ -17502,16 +17519,16 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>449</v>
@@ -17525,16 +17542,16 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>449</v>
@@ -17548,16 +17565,16 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>449</v>
@@ -17571,16 +17588,16 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>449</v>
@@ -17594,16 +17611,16 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>449</v>
@@ -17617,16 +17634,16 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>449</v>
@@ -17640,16 +17657,16 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>449</v>
@@ -17663,16 +17680,16 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>449</v>
@@ -17686,16 +17703,16 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>449</v>
@@ -17709,16 +17726,16 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>449</v>
@@ -17732,16 +17749,16 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>449</v>
@@ -17755,16 +17772,16 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>449</v>
@@ -17778,16 +17795,16 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>449</v>
@@ -17801,16 +17818,16 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>449</v>
@@ -17824,16 +17841,16 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>449</v>
@@ -17847,16 +17864,16 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>449</v>
@@ -17870,16 +17887,16 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>449</v>
@@ -17893,16 +17910,16 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>449</v>
@@ -17916,16 +17933,16 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>449</v>
@@ -17939,16 +17956,16 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>449</v>
@@ -17962,7 +17979,7 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>341</v>
@@ -17971,7 +17988,7 @@
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>449</v>
@@ -17985,16 +18002,16 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>449</v>
@@ -18008,16 +18025,16 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>449</v>
@@ -18031,16 +18048,16 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>449</v>
@@ -18054,16 +18071,16 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>449</v>
@@ -18077,16 +18094,16 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>449</v>
@@ -18100,16 +18117,16 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>449</v>
@@ -18123,16 +18140,16 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>449</v>
@@ -18146,16 +18163,16 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>449</v>
@@ -18169,7 +18186,7 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>9</v>
@@ -18178,7 +18195,7 @@
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>449</v>
@@ -18192,16 +18209,16 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>449</v>
@@ -18215,16 +18232,16 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>449</v>
@@ -18239,16 +18256,16 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>449</v>
@@ -18262,7 +18279,7 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>444</v>
@@ -18271,7 +18288,7 @@
         <v>10</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>449</v>
@@ -18285,7 +18302,7 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>419</v>
@@ -18294,7 +18311,7 @@
         <v>10</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>449</v>
@@ -18308,16 +18325,16 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>449</v>
@@ -18331,16 +18348,16 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>449</v>
@@ -18354,16 +18371,16 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>449</v>
@@ -18377,16 +18394,16 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>449</v>
@@ -18400,16 +18417,16 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>449</v>
@@ -18423,7 +18440,7 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>23</v>
@@ -18435,7 +18452,7 @@
         <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="H62" s="2">
         <v>10.0</v>
@@ -18446,16 +18463,16 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>449</v>
@@ -18469,16 +18486,16 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>449</v>
@@ -18492,16 +18509,16 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>449</v>
@@ -18515,7 +18532,7 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>475</v>
@@ -18524,7 +18541,7 @@
         <v>10</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>449</v>
@@ -18538,16 +18555,16 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>449</v>
@@ -18561,16 +18578,16 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>449</v>
@@ -18580,23 +18597,52 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" s="2">
+        <v>68.0</v>
+      </c>
       <c r="B69" s="2" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>449</v>
       </c>
       <c r="H69" s="2">
         <v>10.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2">
+        <v>69.0</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="H70" s="2">
+        <v>8.0</v>
       </c>
     </row>
   </sheetData>
@@ -18657,22 +18703,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H2" s="1">
         <v>4.0</v>
@@ -18683,22 +18729,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -18709,22 +18755,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -18735,22 +18781,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -18761,22 +18807,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
@@ -18787,19 +18833,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H7" s="1">
         <v>4.0</v>
@@ -18810,22 +18856,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H8" s="1">
         <v>4.0</v>
@@ -18836,22 +18882,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H9" s="1">
         <v>4.0</v>
@@ -18862,22 +18908,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H10" s="1">
         <v>4.0</v>
@@ -18888,22 +18934,22 @@
         <v>12.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H11" s="2">
         <v>3.0</v>
@@ -18914,22 +18960,22 @@
         <v>31.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H12" s="2">
         <v>4.0</v>
@@ -18940,22 +18986,22 @@
         <v>78.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -18966,10 +19012,10 @@
         <v>10.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
@@ -18978,10 +19024,10 @@
         <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H14" s="2">
         <v>9.0</v>
@@ -18992,10 +19038,10 @@
         <v>11.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
@@ -19004,10 +19050,10 @@
         <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H15" s="2">
         <v>6.0</v>
@@ -19018,10 +19064,10 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
@@ -19030,10 +19076,10 @@
         <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H16" s="2">
         <v>6.0</v>
@@ -19044,10 +19090,10 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
@@ -19067,10 +19113,10 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
@@ -19079,10 +19125,10 @@
         <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H18" s="2">
         <v>6.0</v>
@@ -19093,10 +19139,10 @@
         <v>16.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -19105,10 +19151,10 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -19119,10 +19165,10 @@
         <v>17.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
@@ -19131,10 +19177,10 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -19145,10 +19191,10 @@
         <v>18.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
@@ -19157,10 +19203,10 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -19171,10 +19217,10 @@
         <v>19.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -19183,10 +19229,10 @@
         <v>16</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -19197,10 +19243,10 @@
         <v>20.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -19209,10 +19255,10 @@
         <v>16</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H23" s="2">
         <v>6.0</v>
@@ -19223,10 +19269,10 @@
         <v>21.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
@@ -19246,10 +19292,10 @@
         <v>22.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
@@ -19269,10 +19315,10 @@
         <v>23.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>10</v>
@@ -19292,10 +19338,10 @@
         <v>24.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
@@ -19315,10 +19361,10 @@
         <v>25.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
@@ -19327,10 +19373,10 @@
         <v>16</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -19341,10 +19387,10 @@
         <v>26.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
@@ -19364,10 +19410,10 @@
         <v>27.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
@@ -19387,10 +19433,10 @@
         <v>28.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>10</v>
@@ -19410,10 +19456,10 @@
         <v>29.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>10</v>
@@ -19433,22 +19479,22 @@
         <v>30.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -19459,16 +19505,16 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>12</v>
@@ -19482,16 +19528,16 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>12</v>
@@ -19505,22 +19551,22 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -19531,16 +19577,16 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>12</v>
@@ -19554,16 +19600,16 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>12</v>
@@ -19577,16 +19623,16 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>12</v>
@@ -19600,16 +19646,16 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>12</v>
@@ -19623,16 +19669,16 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>12</v>
@@ -19646,16 +19692,16 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>12</v>
@@ -19669,16 +19715,16 @@
         <v>41.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>12</v>
@@ -19692,16 +19738,16 @@
         <v>42.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>12</v>
@@ -19715,7 +19761,7 @@
         <v>43.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>23</v>
@@ -19724,7 +19770,7 @@
         <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>12</v>
@@ -19738,16 +19784,16 @@
         <v>44.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>12</v>
@@ -19761,22 +19807,22 @@
         <v>45.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H47" s="2">
         <v>9.0</v>
@@ -19787,22 +19833,22 @@
         <v>46.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -19813,7 +19859,7 @@
         <v>47.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>9</v>
@@ -19822,13 +19868,13 @@
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H49" s="2">
         <v>6.0</v>
@@ -19839,22 +19885,22 @@
         <v>48.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -19865,22 +19911,22 @@
         <v>49.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H51" s="2">
         <v>9.0</v>
@@ -19891,22 +19937,22 @@
         <v>50.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H52" s="2">
         <v>9.0</v>
@@ -19917,16 +19963,16 @@
         <v>51.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>12</v>
@@ -19940,16 +19986,16 @@
         <v>52.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>12</v>
@@ -19963,16 +20009,16 @@
         <v>53.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>12</v>
@@ -19986,22 +20032,22 @@
         <v>54.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H56" s="2">
         <v>9.0</v>
@@ -20012,16 +20058,16 @@
         <v>55.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>12</v>
@@ -20035,22 +20081,22 @@
         <v>56.0</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H58" s="2">
         <v>9.0</v>
@@ -20061,22 +20107,22 @@
         <v>57.0</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H59" s="2">
         <v>9.0</v>
@@ -20087,22 +20133,22 @@
         <v>58.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H60" s="2">
         <v>9.0</v>
@@ -20113,22 +20159,22 @@
         <v>59.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H61" s="2">
         <v>9.0</v>
@@ -20139,22 +20185,22 @@
         <v>60.0</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H62" s="2">
         <v>9.0</v>
@@ -20165,22 +20211,22 @@
         <v>61.0</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H63" s="2">
         <v>9.0</v>
@@ -20191,22 +20237,22 @@
         <v>62.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H64" s="2">
         <v>9.0</v>
@@ -20217,22 +20263,22 @@
         <v>63.0</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H65" s="2">
         <v>9.0</v>
@@ -20243,22 +20289,22 @@
         <v>64.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H66" s="2">
         <v>9.0</v>
@@ -20269,22 +20315,22 @@
         <v>65.0</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H67" s="2">
         <v>9.0</v>
@@ -20295,22 +20341,22 @@
         <v>66.0</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H68" s="2">
         <v>9.0</v>
@@ -20321,22 +20367,22 @@
         <v>67.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H69" s="2">
         <v>9.0</v>
@@ -20347,22 +20393,22 @@
         <v>68.0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H70" s="2">
         <v>6.0</v>
@@ -20373,22 +20419,22 @@
         <v>69.0</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H71" s="2">
         <v>6.0</v>
@@ -20399,22 +20445,22 @@
         <v>70.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H72" s="2">
         <v>9.0</v>
@@ -20425,22 +20471,22 @@
         <v>71.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H73" s="2">
         <v>9.0</v>
@@ -20451,16 +20497,16 @@
         <v>72.0</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>12</v>
@@ -20474,16 +20520,16 @@
         <v>73.0</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>12</v>
@@ -20497,22 +20543,22 @@
         <v>74.0</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H76" s="2">
         <v>6.0</v>
@@ -20523,16 +20569,16 @@
         <v>75.0</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>12</v>
@@ -20546,16 +20592,16 @@
         <v>76.0</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>12</v>
@@ -20569,16 +20615,16 @@
         <v>77.0</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>12</v>
@@ -20592,22 +20638,22 @@
         <v>78.0</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H80" s="2">
         <v>9.0</v>
@@ -20618,22 +20664,22 @@
         <v>79.0</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H81" s="2">
         <v>9.0</v>
@@ -20644,22 +20690,22 @@
         <v>80.0</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H82" s="2">
         <v>9.0</v>
@@ -20670,22 +20716,22 @@
         <v>81.0</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H83" s="2">
         <v>9.0</v>
@@ -20696,16 +20742,16 @@
         <v>82.0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>334</v>
+        <v>10</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>12</v>
@@ -20803,13 +20849,13 @@
         <v>348</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>349</v>
@@ -20829,13 +20875,13 @@
         <v>351</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>352</v>
@@ -20855,13 +20901,13 @@
         <v>354</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>12</v>
@@ -20881,13 +20927,13 @@
         <v>356</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>12</v>
@@ -21876,7 +21922,7 @@
         <v>359</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>360</v>
@@ -21899,10 +21945,10 @@
         <v>363</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>364</v>
@@ -21925,10 +21971,10 @@
         <v>367</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>368</v>
@@ -21951,7 +21997,7 @@
         <v>371</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>11</v>
@@ -21974,13 +22020,13 @@
         <v>374</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>375</v>
@@ -22000,13 +22046,13 @@
         <v>377</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>378</v>
@@ -22032,7 +22078,7 @@
         <v>382</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>383</v>
@@ -22052,13 +22098,13 @@
         <v>385</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>382</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>386</v>
@@ -22104,13 +22150,13 @@
         <v>391</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>392</v>
@@ -22130,13 +22176,13 @@
         <v>394</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>395</v>
@@ -22188,7 +22234,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>403</v>
@@ -22208,13 +22254,13 @@
         <v>405</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>406</v>
@@ -22234,7 +22280,7 @@
         <v>408</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
@@ -22266,7 +22312,7 @@
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>413</v>
@@ -22286,13 +22332,13 @@
         <v>415</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>416</v>
@@ -22318,7 +22364,7 @@
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>420</v>
@@ -22338,7 +22384,7 @@
         <v>422</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
@@ -22367,7 +22413,7 @@
         <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>12</v>
@@ -22413,7 +22459,7 @@
         <v>429</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -22445,7 +22491,7 @@
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>434</v>
@@ -22465,13 +22511,13 @@
         <v>436</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>437</v>
@@ -22491,13 +22537,13 @@
         <v>439</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>440</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>441</v>
@@ -22523,7 +22569,7 @@
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>445</v>
@@ -22575,7 +22621,7 @@
         <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>453</v>
@@ -22595,13 +22641,13 @@
         <v>455</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>449</v>
@@ -22653,7 +22699,7 @@
         <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>462</v>
@@ -22699,13 +22745,13 @@
         <v>468</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>469</v>
@@ -22725,13 +22771,13 @@
         <v>471</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>472</v>
@@ -22757,7 +22803,7 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>476</v>
@@ -22832,7 +22878,7 @@
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>487</v>
@@ -22852,13 +22898,13 @@
         <v>489</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>490</v>
@@ -22904,7 +22950,7 @@
         <v>495</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
@@ -22930,7 +22976,7 @@
         <v>497</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
@@ -22956,13 +23002,13 @@
         <v>499</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>449</v>
@@ -22979,16 +23025,19 @@
         <v>500</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>501</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>502</v>
       </c>
       <c r="H45" s="2">
         <v>6.0</v>
@@ -22999,10 +23048,10 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
@@ -23012,6 +23061,9 @@
       </c>
       <c r="F46" s="2" t="s">
         <v>449</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>504</v>
       </c>
       <c r="H46" s="2">
         <v>9.0</v>
@@ -23022,19 +23074,19 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="H47" s="2">
         <v>6.0</v>
@@ -23045,10 +23097,10 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
@@ -23060,7 +23112,7 @@
         <v>449</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -23071,22 +23123,22 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="H49" s="2">
         <v>9.0</v>
@@ -23097,22 +23149,22 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>449</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -24128,22 +24180,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -24154,22 +24206,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -24180,22 +24232,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -24206,22 +24258,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -24232,22 +24284,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -24258,22 +24310,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -24284,22 +24336,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H8" s="2">
         <v>4.0</v>
@@ -24310,22 +24362,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H9" s="2">
         <v>6.0</v>
@@ -24336,22 +24388,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -24362,22 +24414,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -24388,22 +24440,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H12" s="2">
         <v>5.0</v>
@@ -24414,22 +24466,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H13" s="2">
         <v>3.0</v>
@@ -24440,10 +24492,10 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
@@ -24463,10 +24515,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
@@ -24475,10 +24527,10 @@
         <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -24489,22 +24541,22 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -24515,7 +24567,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>367</v>
@@ -24530,7 +24582,7 @@
         <v>449</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H17" s="2">
         <v>9.0</v>
@@ -24541,22 +24593,22 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -24567,22 +24619,22 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>430</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -24593,22 +24645,22 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="H20" s="2">
         <v>7.0</v>
@@ -24619,7 +24671,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>458</v>
@@ -24628,13 +24680,13 @@
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>449</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="H21" s="2">
         <v>7.0</v>
@@ -24645,10 +24697,10 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -24660,7 +24712,7 @@
         <v>449</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -24671,19 +24723,19 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -24694,10 +24746,10 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
@@ -24709,7 +24761,7 @@
         <v>449</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -24720,10 +24772,10 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -24732,10 +24784,10 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -24746,10 +24798,10 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -24758,10 +24810,10 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="H26" s="2">
         <v>9.0</v>
@@ -24772,10 +24824,10 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
@@ -24784,10 +24836,10 @@
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -25826,22 +25878,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -25852,22 +25904,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="H3" s="2">
         <v>7.0</v>
@@ -25878,22 +25930,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -25904,22 +25956,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -25930,22 +25982,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -25956,22 +26008,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -25982,10 +26034,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
@@ -26005,7 +26057,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>381</v>
@@ -26014,13 +26066,13 @@
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -26031,10 +26083,10 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
@@ -27095,22 +27147,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H2" s="2">
         <v>2.0</v>
@@ -27121,22 +27173,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -27147,22 +27199,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -27173,22 +27225,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="H5" s="1">
         <v>5.0</v>
@@ -27199,22 +27251,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -27225,7 +27277,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>433</v>
@@ -27234,13 +27286,13 @@
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>
@@ -27251,16 +27303,16 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>449</v>
@@ -27274,10 +27326,10 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
@@ -27289,7 +27341,7 @@
         <v>453</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -27300,16 +27352,16 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>449</v>
@@ -27323,22 +27375,22 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -27349,22 +27401,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -27375,10 +27427,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -27387,10 +27439,10 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H13" s="2">
         <v>9.0</v>
@@ -28438,22 +28490,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -28464,22 +28516,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -28490,22 +28542,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -28516,10 +28568,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -28539,22 +28591,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -28565,7 +28617,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>479</v>
@@ -28574,13 +28626,13 @@
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -28591,22 +28643,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="H8" s="2">
         <v>5.0</v>
@@ -29660,22 +29712,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -29686,22 +29738,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -29712,19 +29764,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -29735,22 +29787,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -29761,22 +29813,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="H6" s="2">
         <v>7.0</v>
@@ -29787,10 +29839,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -29799,10 +29851,10 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="902">
   <si>
     <t>id</t>
   </si>
@@ -1590,6 +1590,15 @@
   </si>
   <si>
     <t>./public/member-images/2023/PHAM_TRUONG_BAO_HOANG.webp</t>
+  </si>
+  <si>
+    <t>Trần Thị Thanh Tuyền</t>
+  </si>
+  <si>
+    <t>Nậnn</t>
+  </si>
+  <si>
+    <t>./public/member-images/2023/TRAN_THI_THANH_TUYEN.webp</t>
   </si>
   <si>
     <t>Phan Thị Phương Anh (Sô)</t>
@@ -4518,10 +4527,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -4530,10 +4539,10 @@
         <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -4544,22 +4553,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="H3" s="2">
         <v>2.0</v>
@@ -4570,7 +4579,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>402</v>
@@ -4582,10 +4591,10 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="H4" s="2">
         <v>6.0</v>
@@ -4596,22 +4605,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="H5" s="1">
         <v>3.0</v>
@@ -4622,22 +4631,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>322</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -4648,10 +4657,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -4660,10 +4669,10 @@
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="H7" s="1">
         <v>6.0</v>
@@ -4674,22 +4683,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>183</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -4700,22 +4709,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>133</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -4726,7 +4735,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>203</v>
@@ -4735,7 +4744,7 @@
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>449</v>
@@ -5787,22 +5796,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6857,22 +6866,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6883,10 +6892,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -6895,10 +6904,10 @@
         <v>55</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -7952,22 +7961,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>419</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="H2" s="7">
         <v>5.0</v>
@@ -9022,19 +9031,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -9045,16 +9054,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>449</v>
@@ -10114,22 +10123,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>190</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -10140,22 +10149,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>309</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -10166,7 +10175,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>103</v>
@@ -10178,10 +10187,10 @@
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="H4" s="2">
         <v>4.0</v>
@@ -10192,22 +10201,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>218</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -11261,10 +11270,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -11273,10 +11282,10 @@
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -11287,22 +11296,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -11313,22 +11322,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>483</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -11339,7 +11348,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>112</v>
@@ -11351,10 +11360,10 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="H5" s="1">
         <v>6.0</v>
@@ -11365,7 +11374,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>264</v>
@@ -11377,10 +11386,10 @@
         <v>55</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="H6" s="2">
         <v>6.0</v>
@@ -12403,7 +12412,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -14515,22 +14524,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>167</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="H2" s="2">
         <v>8.0</v>
@@ -14541,16 +14550,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>796</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>793</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>449</v>
@@ -14564,22 +14573,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>250</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>449</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="H4" s="2">
         <v>8.0</v>
@@ -14590,16 +14599,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>103</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>449</v>
@@ -14613,16 +14622,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>449</v>
@@ -17050,22 +17059,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>38</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -17076,13 +17085,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -17091,7 +17100,7 @@
         <v>449</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="H3" s="2">
         <v>7.0</v>
@@ -17102,13 +17111,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>11</v>
@@ -17117,7 +17126,7 @@
         <v>449</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -17128,13 +17137,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>103</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>46</v>
@@ -17151,16 +17160,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>449</v>
@@ -17174,16 +17183,16 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>449</v>
@@ -17197,10 +17206,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -17209,7 +17218,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
@@ -17220,16 +17229,16 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>449</v>
@@ -17243,16 +17252,16 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>449</v>
@@ -17266,7 +17275,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>23</v>
@@ -17275,7 +17284,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>449</v>
@@ -17289,7 +17298,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>363</v>
@@ -17298,7 +17307,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>449</v>
@@ -17312,7 +17321,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>188</v>
@@ -17321,7 +17330,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>449</v>
@@ -17335,7 +17344,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>163</v>
@@ -17344,7 +17353,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>449</v>
@@ -17358,7 +17367,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>305</v>
@@ -17367,7 +17376,7 @@
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>449</v>
@@ -17381,7 +17390,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>210</v>
@@ -17390,7 +17399,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>449</v>
@@ -17404,7 +17413,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>133</v>
@@ -17413,7 +17422,7 @@
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>449</v>
@@ -17427,16 +17436,16 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>449</v>
@@ -17450,7 +17459,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>59</v>
@@ -17459,7 +17468,7 @@
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>449</v>
@@ -17473,7 +17482,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>42</v>
@@ -17496,7 +17505,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>309</v>
@@ -17519,7 +17528,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>94</v>
@@ -17528,7 +17537,7 @@
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>449</v>
@@ -17542,7 +17551,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>223</v>
@@ -17551,7 +17560,7 @@
         <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>449</v>
@@ -17565,16 +17574,16 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>449</v>
@@ -17588,7 +17597,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>129</v>
@@ -17597,7 +17606,7 @@
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>449</v>
@@ -17611,7 +17620,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>218</v>
@@ -17620,7 +17629,7 @@
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>449</v>
@@ -17634,7 +17643,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>220</v>
@@ -17643,7 +17652,7 @@
         <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>449</v>
@@ -17657,16 +17666,16 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>449</v>
@@ -17680,16 +17689,16 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>449</v>
@@ -17703,7 +17712,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>31</v>
@@ -17712,7 +17721,7 @@
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>449</v>
@@ -17726,16 +17735,16 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>449</v>
@@ -17749,7 +17758,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>42</v>
@@ -17758,7 +17767,7 @@
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>449</v>
@@ -17781,7 +17790,7 @@
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>449</v>
@@ -17795,7 +17804,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>73</v>
@@ -17804,7 +17813,7 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>449</v>
@@ -17818,16 +17827,16 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>449</v>
@@ -17841,16 +17850,16 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>449</v>
@@ -17864,7 +17873,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>192</v>
@@ -17873,7 +17882,7 @@
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>449</v>
@@ -17887,16 +17896,16 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>449</v>
@@ -17910,16 +17919,16 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>449</v>
@@ -17933,16 +17942,16 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>449</v>
@@ -17956,16 +17965,16 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>449</v>
@@ -17979,7 +17988,7 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>341</v>
@@ -17988,7 +17997,7 @@
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>449</v>
@@ -18002,7 +18011,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>320</v>
@@ -18025,16 +18034,16 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>449</v>
@@ -18048,7 +18057,7 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>313</v>
@@ -18057,7 +18066,7 @@
         <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>449</v>
@@ -18071,16 +18080,16 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>449</v>
@@ -18094,16 +18103,16 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>449</v>
@@ -18117,16 +18126,16 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>449</v>
@@ -18140,7 +18149,7 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>129</v>
@@ -18149,7 +18158,7 @@
         <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>449</v>
@@ -18163,16 +18172,16 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>449</v>
@@ -18186,7 +18195,7 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>9</v>
@@ -18195,7 +18204,7 @@
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>449</v>
@@ -18209,7 +18218,7 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>66</v>
@@ -18218,7 +18227,7 @@
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>449</v>
@@ -18232,16 +18241,16 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>449</v>
@@ -18256,16 +18265,16 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>449</v>
@@ -18279,7 +18288,7 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>444</v>
@@ -18288,7 +18297,7 @@
         <v>10</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>449</v>
@@ -18302,7 +18311,7 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>419</v>
@@ -18311,7 +18320,7 @@
         <v>10</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>449</v>
@@ -18325,16 +18334,16 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>449</v>
@@ -18348,16 +18357,16 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>449</v>
@@ -18371,7 +18380,7 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>188</v>
@@ -18380,7 +18389,7 @@
         <v>10</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>449</v>
@@ -18394,7 +18403,7 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>66</v>
@@ -18403,7 +18412,7 @@
         <v>10</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>449</v>
@@ -18417,7 +18426,7 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>167</v>
@@ -18426,7 +18435,7 @@
         <v>10</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>449</v>
@@ -18440,7 +18449,7 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>23</v>
@@ -18452,7 +18461,7 @@
         <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="H62" s="2">
         <v>10.0</v>
@@ -18463,7 +18472,7 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>54</v>
@@ -18472,7 +18481,7 @@
         <v>10</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>449</v>
@@ -18486,16 +18495,16 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>449</v>
@@ -18509,16 +18518,16 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>449</v>
@@ -18532,7 +18541,7 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>475</v>
@@ -18541,7 +18550,7 @@
         <v>10</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>449</v>
@@ -18555,7 +18564,7 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>250</v>
@@ -18564,7 +18573,7 @@
         <v>10</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>449</v>
@@ -18578,16 +18587,16 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>449</v>
@@ -18601,7 +18610,7 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>250</v>
@@ -18610,7 +18619,7 @@
         <v>10</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>449</v>
@@ -18624,22 +18633,22 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="H70" s="2">
         <v>8.0</v>
@@ -23170,7 +23179,32 @@
         <v>9.0</v>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="H51" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
     <row r="52" ht="15.75" customHeight="1"/>
     <row r="53" ht="15.75" customHeight="1"/>
     <row r="54" ht="15.75" customHeight="1"/>
@@ -24180,22 +24214,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>103</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -24206,10 +24240,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>108</v>
@@ -24218,10 +24252,10 @@
         <v>38</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -24232,7 +24266,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>129</v>
@@ -24244,10 +24278,10 @@
         <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -24258,22 +24292,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -24284,22 +24318,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -24310,22 +24344,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>210</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -24336,10 +24370,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>108</v>
@@ -24348,10 +24382,10 @@
         <v>38</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="H8" s="2">
         <v>4.0</v>
@@ -24362,22 +24396,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="H9" s="2">
         <v>6.0</v>
@@ -24388,7 +24422,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>301</v>
@@ -24400,10 +24434,10 @@
         <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -24414,7 +24448,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>313</v>
@@ -24426,10 +24460,10 @@
         <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -24440,22 +24474,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H12" s="2">
         <v>5.0</v>
@@ -24466,22 +24500,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="H13" s="2">
         <v>3.0</v>
@@ -24492,7 +24526,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>59</v>
@@ -24515,10 +24549,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
@@ -24527,10 +24561,10 @@
         <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -24541,10 +24575,10 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
@@ -24553,10 +24587,10 @@
         <v>38</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -24567,7 +24601,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>367</v>
@@ -24582,7 +24616,7 @@
         <v>449</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="H17" s="2">
         <v>9.0</v>
@@ -24593,10 +24627,10 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
@@ -24605,10 +24639,10 @@
         <v>46</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -24619,10 +24653,10 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -24634,7 +24668,7 @@
         <v>430</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -24645,22 +24679,22 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="H20" s="2">
         <v>7.0</v>
@@ -24671,7 +24705,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>458</v>
@@ -24686,7 +24720,7 @@
         <v>449</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="H21" s="2">
         <v>7.0</v>
@@ -24697,7 +24731,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>218</v>
@@ -24712,7 +24746,7 @@
         <v>449</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -24723,10 +24757,10 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -24735,7 +24769,7 @@
         <v>55</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -24746,7 +24780,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>112</v>
@@ -24761,7 +24795,7 @@
         <v>449</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -24772,7 +24806,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>305</v>
@@ -24784,10 +24818,10 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -24798,10 +24832,10 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -24810,10 +24844,10 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="H26" s="2">
         <v>9.0</v>
@@ -24824,7 +24858,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>210</v>
@@ -24836,10 +24870,10 @@
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -25878,7 +25912,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>54</v>
@@ -25890,10 +25924,10 @@
         <v>38</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -25904,22 +25938,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>112</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="H3" s="2">
         <v>7.0</v>
@@ -25930,22 +25964,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -25956,7 +25990,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>228</v>
@@ -25968,10 +26002,10 @@
         <v>55</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -25982,22 +26016,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>167</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -26008,22 +26042,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>129</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -26034,7 +26068,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>59</v>
@@ -26057,7 +26091,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>381</v>
@@ -26069,10 +26103,10 @@
         <v>55</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -26083,7 +26117,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>59</v>
@@ -27147,22 +27181,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="H2" s="2">
         <v>2.0</v>
@@ -27173,22 +27207,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>210</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -27199,22 +27233,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -27225,22 +27259,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="H5" s="1">
         <v>5.0</v>
@@ -27251,22 +27285,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -27277,7 +27311,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>433</v>
@@ -27289,10 +27323,10 @@
         <v>38</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>
@@ -27303,10 +27337,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
@@ -27326,7 +27360,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>309</v>
@@ -27341,7 +27375,7 @@
         <v>453</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -27352,7 +27386,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>309</v>
@@ -27375,7 +27409,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>103</v>
@@ -27387,10 +27421,10 @@
         <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -27401,7 +27435,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>103</v>
@@ -27413,10 +27447,10 @@
         <v>55</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -27427,10 +27461,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -27439,10 +27473,10 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="H13" s="2">
         <v>9.0</v>
@@ -28490,22 +28524,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -28516,22 +28550,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -28542,22 +28576,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -28568,10 +28602,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -28591,7 +28625,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>305</v>
@@ -28603,10 +28637,10 @@
         <v>55</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -28617,7 +28651,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>479</v>
@@ -28629,10 +28663,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -28643,22 +28677,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="H8" s="2">
         <v>5.0</v>
@@ -29712,10 +29746,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -29724,10 +29758,10 @@
         <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -29738,22 +29772,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -29764,7 +29798,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>226</v>
@@ -29776,7 +29810,7 @@
         <v>46</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -29787,22 +29821,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -29813,22 +29847,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>167</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H6" s="2">
         <v>7.0</v>
@@ -29839,7 +29873,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>99</v>
@@ -29851,10 +29885,10 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="907">
   <si>
     <t>id</t>
   </si>
@@ -337,6 +337,9 @@
     <t>Lê Thị Trà My</t>
   </si>
   <si>
+    <t>./public/member-images/2025/LE_THI_TRA_MY.webp</t>
+  </si>
+  <si>
     <t>Hồ Thị Minh Châu (cún)</t>
   </si>
   <si>
@@ -425,6 +428,9 @@
   </si>
   <si>
     <t>JKL</t>
+  </si>
+  <si>
+    <t>./public/member-images/2024/PHAM_DUC_DINH.webp</t>
   </si>
   <si>
     <t>Trần Nguyễn Ánh Nhi</t>
@@ -708,9 +714,15 @@
     <t>Kiệt</t>
   </si>
   <si>
+    <t>./public/member-images/2024/HO_DAC_ANH_KIET.webp</t>
+  </si>
+  <si>
     <t>Vĩnh Phúc</t>
   </si>
   <si>
+    <t>./public/member-images/2024/VINH_PHUC.webp</t>
+  </si>
+  <si>
     <t>Lê Uyên Thi</t>
   </si>
   <si>
@@ -724,6 +736,9 @@
   </si>
   <si>
     <t>Hào</t>
+  </si>
+  <si>
+    <t>./public/member-images/2024/LE_CHI_NHAT_HAO.webp</t>
   </si>
   <si>
     <t>Nguyễn Mai Thùy Trâm</t>
@@ -1592,274 +1607,274 @@
     <t>./public/member-images/2023/PHAM_TRUONG_BAO_HOANG.webp</t>
   </si>
   <si>
+    <t>Phan Thị Phương Anh (Sô)</t>
+  </si>
+  <si>
+    <t>Ban chấp hành 2023-2025</t>
+  </si>
+  <si>
+    <t>Sony Phan</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/PHAN_THI_PHUONG_ANH.webp</t>
+  </si>
+  <si>
+    <t>Trần Thị Hà (Trần Hà)</t>
+  </si>
+  <si>
+    <t>Hà</t>
+  </si>
+  <si>
+    <t>Quảng Hồng</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/TRAN_THI_HA.webp</t>
+  </si>
+  <si>
+    <t>Nguyễn Hồ Thảo Nhi (Pho)</t>
+  </si>
+  <si>
+    <t>trong veo</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/NGUYEN_HO_THAO_NHI.webp</t>
+  </si>
+  <si>
+    <t>Trần  Thị Như Giao</t>
+  </si>
+  <si>
+    <t>Giao</t>
+  </si>
+  <si>
+    <t>Tử tế</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/TRAN_THI_NHU_GIAO.webp</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Ngọc Ánh (Énn énnnnn)</t>
+  </si>
+  <si>
+    <t>Ban chấp hành 2023-2024</t>
+  </si>
+  <si>
+    <t>Mặt trời nhỏo</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/NGUYEN_THI_NGOC_ANH.webp</t>
+  </si>
+  <si>
+    <t>Hồ Thị Châu Linh</t>
+  </si>
+  <si>
+    <t>Ban chấp hành 2022-2025</t>
+  </si>
+  <si>
+    <t>Cá thích chơi</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/HO_THI_CHAU_LINH.webp</t>
+  </si>
+  <si>
+    <t>Dương Thị Thu Huyền</t>
+  </si>
+  <si>
+    <t>Huyền</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;𝘽𝙚 𝙮𝙤𝙪𝙧𝙨𝙚𝙡𝙛, 𝙙𝙤𝙣'𝙩 𝙗𝙚 𝙖𝙣𝙮𝙤𝙣𝙚 𝙚𝙡𝙨𝙚&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/DUONG_THI_THU_HUYEN.webp</t>
+  </si>
+  <si>
+    <t>Hoàng Hữu Tuấn Vũ (TVũ 4S)</t>
+  </si>
+  <si>
+    <t>Vũ</t>
+  </si>
+  <si>
+    <t>Chưa có nhóm</t>
+  </si>
+  <si>
+    <t>Sống chỉ đơn giản - lấy nụ cười làm căn bản</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/HOANG_HUU_TUAN_VU.webp</t>
+  </si>
+  <si>
+    <t>Trần Phương Nam (Nhuận Tường)</t>
+  </si>
+  <si>
+    <t>Hiện tại mình đang sống ẩn</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/TRAN_PHUONG_NAM.webp</t>
+  </si>
+  <si>
+    <t>Võ Hồng Đức (Mai Cồ Phước Duyên)</t>
+  </si>
+  <si>
+    <t>Hậu cần, Diễn kịch và Nước mía</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/VO_HONG_DUC.webp</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Nguyên Thông (Thúng)</t>
+  </si>
+  <si>
+    <t>Thông</t>
+  </si>
+  <si>
+    <t>Trưởng ban truyền thông 2025</t>
+  </si>
+  <si>
+    <t>Thở là ra thơ</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/NGUYEN_DUC_NGUYEN_THONG.webp</t>
+  </si>
+  <si>
+    <t>Đậu Đoàn Hoàn Mỹ (Mỵ Mỵ)</t>
+  </si>
+  <si>
+    <t>Mỹ</t>
+  </si>
+  <si>
+    <t>Trưởng ban văn nghệ, thỉnh sư</t>
+  </si>
+  <si>
+    <t>Nhỏ mà có võ</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/DAU_DOAN_HOAN_MY.webp</t>
+  </si>
+  <si>
+    <t>Lê  Thị Ngọc</t>
+  </si>
+  <si>
+    <t>Lê Thị Thanh Nhàn</t>
+  </si>
+  <si>
+    <t>Nhàn</t>
+  </si>
+  <si>
+    <t>Quảng Thuần</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/LE_THI_THANH_NHAN.webp</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Rin</t>
+  </si>
+  <si>
+    <t>Rin</t>
+  </si>
+  <si>
+    <t>Nguyện Thành</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/NGUYEN_VAN_RIN.webp</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Mỹ Duyên</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/NGUYEN_THI_MY_DUYEN.webp</t>
+  </si>
+  <si>
+    <t>Châu Phước Nhật</t>
+  </si>
+  <si>
+    <t>Nhật</t>
+  </si>
+  <si>
+    <t>Nhuận Tuệ</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/CHAU_PHUOC_NHAT.webp</t>
+  </si>
+  <si>
+    <t>Trần Như Nhã Kỳ</t>
+  </si>
+  <si>
+    <t>Kỳ</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/TRAN_NHU_NHA_KY.webp</t>
+  </si>
+  <si>
+    <t>Lê Thị Diễm My (Mymyno)</t>
+  </si>
+  <si>
+    <t>Nhuận Hiền</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/LE_THI_DIEM_MY.webp</t>
+  </si>
+  <si>
+    <t>Dương Thị Thanh Tâm</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/DUONG_THI_THANH_TAM.webp</t>
+  </si>
+  <si>
+    <t>Hồ Thị Thảo Tiên</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/HO_THI_THAO_TIEN.webp</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Tuyến</t>
+  </si>
+  <si>
+    <t>Tuyến</t>
+  </si>
+  <si>
+    <t>Quảng Phương</t>
+  </si>
+  <si>
+    <t>Đào Thị Bích Thảo</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/DAO_THI_BICH_THAO.webp</t>
+  </si>
+  <si>
+    <t>Hồ Thị Thanh Hiền</t>
+  </si>
+  <si>
+    <t>Nhuận Đức</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/HO_THI_THANH_HIEN.webp</t>
+  </si>
+  <si>
+    <t>Lê Thị Xuân Nhàn (Nhàn Lee)</t>
+  </si>
+  <si>
+    <t>Mình đây tuy chẳng cao sang. Chỉ mong cố gắng, vững vàng mai sau</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/LE_THI_XUAN_NHAN.webp</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Diệp Linh (Nhỏ)</t>
+  </si>
+  <si>
+    <t>smile</t>
+  </si>
+  <si>
+    <t>./public/member-images/2022/NGUYEN_THI_DIEP_LINH.webp</t>
+  </si>
+  <si>
     <t>Trần Thị Thanh Tuyền</t>
   </si>
   <si>
     <t>Nậnn</t>
   </si>
   <si>
-    <t>./public/member-images/2023/TRAN_THI_THANH_TUYEN.webp</t>
-  </si>
-  <si>
-    <t>Phan Thị Phương Anh (Sô)</t>
-  </si>
-  <si>
-    <t>Ban chấp hành 2023-2025</t>
-  </si>
-  <si>
-    <t>Sony Phan</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/PHAN_THI_PHUONG_ANH.webp</t>
-  </si>
-  <si>
-    <t>Trần Thị Hà (Trần Hà)</t>
-  </si>
-  <si>
-    <t>Hà</t>
-  </si>
-  <si>
-    <t>Quảng Hồng</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/TRAN_THI_HA.webp</t>
-  </si>
-  <si>
-    <t>Nguyễn Hồ Thảo Nhi (Pho)</t>
-  </si>
-  <si>
-    <t>trong veo</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/NGUYEN_HO_THAO_NHI.webp</t>
-  </si>
-  <si>
-    <t>Trần  Thị Như Giao</t>
-  </si>
-  <si>
-    <t>Giao</t>
-  </si>
-  <si>
-    <t>Tử tế</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/TRAN_THI_NHU_GIAO.webp</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Ngọc Ánh (Énn énnnnn)</t>
-  </si>
-  <si>
-    <t>Ban chấp hành 2023-2024</t>
-  </si>
-  <si>
-    <t>Mặt trời nhỏo</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/NGUYEN_THI_NGOC_ANH.webp</t>
-  </si>
-  <si>
-    <t>Hồ Thị Châu Linh</t>
-  </si>
-  <si>
-    <t>Ban chấp hành 2022-2025</t>
-  </si>
-  <si>
-    <t>Cá thích chơi</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/HO_THI_CHAU_LINH.webp</t>
-  </si>
-  <si>
-    <t>Dương Thị Thu Huyền</t>
-  </si>
-  <si>
-    <t>Huyền</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;𝘽𝙚 𝙮𝙤𝙪𝙧𝙨𝙚𝙡𝙛, 𝙙𝙤𝙣'𝙩 𝙗𝙚 𝙖𝙣𝙮𝙤𝙣𝙚 𝙚𝙡𝙨𝙚&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/DUONG_THI_THU_HUYEN.webp</t>
-  </si>
-  <si>
-    <t>Hoàng Hữu Tuấn Vũ (TVũ 4S)</t>
-  </si>
-  <si>
-    <t>Vũ</t>
-  </si>
-  <si>
-    <t>Chưa có nhóm</t>
-  </si>
-  <si>
-    <t>Sống chỉ đơn giản - lấy nụ cười làm căn bản</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/HOANG_HUU_TUAN_VU.webp</t>
-  </si>
-  <si>
-    <t>Trần Phương Nam (Nhuận Tường)</t>
-  </si>
-  <si>
-    <t>Hiện tại mình đang sống ẩn</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/TRAN_PHUONG_NAM.webp</t>
-  </si>
-  <si>
-    <t>Võ Hồng Đức (Mai Cồ Phước Duyên)</t>
-  </si>
-  <si>
-    <t>Hậu cần, Diễn kịch và Nước mía</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/VO_HONG_DUC.webp</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Nguyên Thông (Thúng)</t>
-  </si>
-  <si>
-    <t>Thông</t>
-  </si>
-  <si>
-    <t>Trưởng ban truyền thông 2025</t>
-  </si>
-  <si>
-    <t>Thở là ra thơ</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/NGUYEN_DUC_NGUYEN_THONG.webp</t>
-  </si>
-  <si>
-    <t>Đậu Đoàn Hoàn Mỹ (Mỵ Mỵ)</t>
-  </si>
-  <si>
-    <t>Mỹ</t>
-  </si>
-  <si>
-    <t>Trưởng ban văn nghệ, thỉnh sư</t>
-  </si>
-  <si>
-    <t>Nhỏ mà có võ</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/DAU_DOAN_HOAN_MY.webp</t>
-  </si>
-  <si>
-    <t>Lê  Thị Ngọc</t>
-  </si>
-  <si>
-    <t>Lê Thị Thanh Nhàn</t>
-  </si>
-  <si>
-    <t>Nhàn</t>
-  </si>
-  <si>
-    <t>Quảng Thuần</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/LE_THI_THANH_NHAN.webp</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Rin</t>
-  </si>
-  <si>
-    <t>Rin</t>
-  </si>
-  <si>
-    <t>Nguyện Thành</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/NGUYEN_VAN_RIN.webp</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Mỹ Duyên</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/NGUYEN_THI_MY_DUYEN.webp</t>
-  </si>
-  <si>
-    <t>Châu Phước Nhật</t>
-  </si>
-  <si>
-    <t>Nhật</t>
-  </si>
-  <si>
-    <t>Nhuận Tuệ</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/CHAU_PHUOC_NHAT.webp</t>
-  </si>
-  <si>
-    <t>Trần Như Nhã Kỳ</t>
-  </si>
-  <si>
-    <t>Kỳ</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/TRAN_NHU_NHA_KY.webp</t>
-  </si>
-  <si>
-    <t>Lê Thị Diễm My (Mymyno)</t>
-  </si>
-  <si>
-    <t>Nhuận Hiền</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/LE_THI_DIEM_MY.webp</t>
-  </si>
-  <si>
-    <t>Dương Thị Thanh Tâm</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/DUONG_THI_THANH_TAM.webp</t>
-  </si>
-  <si>
-    <t>Hồ Thị Thảo Tiên</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/HO_THI_THAO_TIEN.webp</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Kim Tuyến</t>
-  </si>
-  <si>
-    <t>Tuyến</t>
-  </si>
-  <si>
-    <t>Quảng Phương</t>
-  </si>
-  <si>
-    <t>Đào Thị Bích Thảo</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/DAO_THI_BICH_THAO.webp</t>
-  </si>
-  <si>
-    <t>Hồ Thị Thanh Hiền</t>
-  </si>
-  <si>
-    <t>Nhuận Đức</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/HO_THI_THANH_HIEN.webp</t>
-  </si>
-  <si>
-    <t>Lê Thị Xuân Nhàn (Nhàn Lee)</t>
-  </si>
-  <si>
-    <t>Mình đây tuy chẳng cao sang. Chỉ mong cố gắng, vững vàng mai sau</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/LE_THI_XUAN_NHAN.webp</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Diệp Linh (Nhỏ)</t>
-  </si>
-  <si>
-    <t>smile</t>
-  </si>
-  <si>
-    <t>./public/member-images/2022/NGUYEN_THI_DIEP_LINH.webp</t>
+    <t>./public/member-images/2022/TRAN_THI_THANH_TUYEN.webp</t>
   </si>
   <si>
     <t>Lê Thị Kim Ngân</t>
@@ -2758,7 +2773,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -2766,6 +2781,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -2790,7 +2811,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2798,14 +2819,15 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2814,7 +2836,7 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -4527,10 +4549,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -4539,10 +4561,10 @@
         <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -4553,22 +4575,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="H3" s="2">
         <v>2.0</v>
@@ -4579,10 +4601,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
@@ -4591,10 +4613,10 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="H4" s="2">
         <v>6.0</v>
@@ -4605,22 +4627,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="H5" s="1">
         <v>3.0</v>
@@ -4631,22 +4653,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -4657,10 +4679,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -4669,10 +4691,10 @@
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="H7" s="1">
         <v>6.0</v>
@@ -4683,22 +4705,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -4709,22 +4731,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -4735,19 +4757,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -5796,22 +5818,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6866,22 +6888,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="H2" s="1">
         <v>5.0</v>
@@ -6892,10 +6914,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -6904,10 +6926,10 @@
         <v>55</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -7957,32 +7979,32 @@
       </c>
     </row>
     <row r="2" ht="23.25" customHeight="1">
-      <c r="A2" s="7">
+      <c r="A2" s="8">
         <v>1.0</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>755</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="B2" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="H2" s="7">
+      <c r="F2" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>762</v>
+      </c>
+      <c r="H2" s="8">
         <v>5.0</v>
       </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
     </row>
     <row r="3" ht="15.75" customHeight="1"/>
     <row r="4" ht="15.75" customHeight="1"/>
@@ -9031,19 +9053,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -9054,19 +9076,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -10123,22 +10145,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -10149,22 +10171,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="H3" s="2">
         <v>6.0</v>
@@ -10175,22 +10197,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="H4" s="2">
         <v>4.0</v>
@@ -10201,22 +10223,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -11270,10 +11292,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -11282,10 +11304,10 @@
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -11296,22 +11318,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="H3" s="2">
         <v>5.0</v>
@@ -11322,22 +11344,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="H4" s="2">
         <v>5.0</v>
@@ -11348,10 +11370,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -11360,10 +11382,10 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="H5" s="1">
         <v>6.0</v>
@@ -11374,10 +11396,10 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
@@ -11386,10 +11408,10 @@
         <v>55</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="H6" s="2">
         <v>6.0</v>
@@ -12412,7 +12434,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -14524,22 +14546,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="H2" s="2">
         <v>8.0</v>
@@ -14550,19 +14572,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>795</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H3" s="2">
         <v>8.0</v>
@@ -14573,22 +14595,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>796</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="H4" s="2">
         <v>8.0</v>
@@ -14599,19 +14621,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H5" s="2">
         <v>8.0</v>
@@ -14622,19 +14644,19 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H6" s="2">
         <v>8.0</v>
@@ -15661,30 +15683,48 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1">
@@ -15754,7 +15794,7 @@
       <c r="E4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -15965,6 +16005,9 @@
       <c r="F12" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="G12" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="H12" s="2">
         <v>9.0</v>
       </c>
@@ -15974,10 +16017,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -15986,10 +16029,10 @@
         <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -16000,10 +16043,10 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
@@ -16012,10 +16055,10 @@
         <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H14" s="2">
         <v>9.0</v>
@@ -17059,22 +17102,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>38</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -17085,22 +17128,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="H3" s="2">
         <v>7.0</v>
@@ -17111,22 +17154,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -17137,19 +17180,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H5" s="2">
         <v>7.0</v>
@@ -17160,19 +17203,19 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
@@ -17183,19 +17226,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
@@ -17206,10 +17249,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -17218,7 +17261,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
@@ -17229,19 +17272,19 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
@@ -17252,19 +17295,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
@@ -17275,7 +17318,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>23</v>
@@ -17284,10 +17327,10 @@
         <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
@@ -17298,19 +17341,19 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H12" s="2">
         <v>10.0</v>
@@ -17321,19 +17364,19 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
@@ -17344,19 +17387,19 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
@@ -17367,19 +17410,19 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
@@ -17390,19 +17433,19 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
@@ -17413,19 +17456,19 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
@@ -17436,19 +17479,19 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
@@ -17459,7 +17502,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>59</v>
@@ -17468,10 +17511,10 @@
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
@@ -17482,7 +17525,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>42</v>
@@ -17494,7 +17537,7 @@
         <v>38</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
@@ -17505,10 +17548,10 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -17517,7 +17560,7 @@
         <v>38</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
@@ -17528,7 +17571,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>94</v>
@@ -17537,10 +17580,10 @@
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
@@ -17551,19 +17594,19 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
@@ -17574,19 +17617,19 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
@@ -17597,19 +17640,19 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
@@ -17620,19 +17663,19 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H26" s="2">
         <v>10.0</v>
@@ -17643,19 +17686,19 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
@@ -17666,19 +17709,19 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
@@ -17689,19 +17732,19 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
@@ -17712,7 +17755,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>31</v>
@@ -17721,10 +17764,10 @@
         <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
@@ -17735,19 +17778,19 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H31" s="2">
         <v>10.0</v>
@@ -17758,7 +17801,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>42</v>
@@ -17767,10 +17810,10 @@
         <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H32" s="2">
         <v>10.0</v>
@@ -17781,19 +17824,19 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
@@ -17804,7 +17847,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>73</v>
@@ -17813,10 +17856,10 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H34" s="2">
         <v>10.0</v>
@@ -17827,19 +17870,19 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
@@ -17850,19 +17893,19 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
@@ -17873,19 +17916,19 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
@@ -17896,19 +17939,19 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H38" s="2">
         <v>10.0</v>
@@ -17919,19 +17962,19 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
@@ -17942,19 +17985,19 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H40" s="2">
         <v>10.0</v>
@@ -17965,19 +18008,19 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
@@ -17988,19 +18031,19 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
@@ -18011,10 +18054,10 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
@@ -18023,7 +18066,7 @@
         <v>28</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H43" s="2">
         <v>10.0</v>
@@ -18034,19 +18077,19 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
@@ -18057,19 +18100,19 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H45" s="2">
         <v>10.0</v>
@@ -18080,19 +18123,19 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
@@ -18103,19 +18146,19 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H47" s="2">
         <v>10.0</v>
@@ -18126,19 +18169,19 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H48" s="2">
         <v>10.0</v>
@@ -18149,19 +18192,19 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H49" s="2">
         <v>10.0</v>
@@ -18172,19 +18215,19 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H50" s="2">
         <v>10.0</v>
@@ -18195,7 +18238,7 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>9</v>
@@ -18204,10 +18247,10 @@
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H51" s="2">
         <v>10.0</v>
@@ -18218,7 +18261,7 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>66</v>
@@ -18227,10 +18270,10 @@
         <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H52" s="2">
         <v>10.0</v>
@@ -18241,21 +18284,21 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>880</v>
-      </c>
-      <c r="D53" s="9" t="s">
+        <v>885</v>
+      </c>
+      <c r="D53" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="G53" s="9"/>
+      <c r="E53" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="G53" s="10"/>
       <c r="H53" s="2">
         <v>10.0</v>
       </c>
@@ -18265,19 +18308,19 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H54" s="2">
         <v>10.0</v>
@@ -18288,19 +18331,19 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H55" s="2">
         <v>10.0</v>
@@ -18311,19 +18354,19 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H56" s="2">
         <v>10.0</v>
@@ -18334,19 +18377,19 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H57" s="2">
         <v>10.0</v>
@@ -18357,19 +18400,19 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H58" s="2">
         <v>10.0</v>
@@ -18380,19 +18423,19 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H59" s="2">
         <v>10.0</v>
@@ -18403,7 +18446,7 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>66</v>
@@ -18412,10 +18455,10 @@
         <v>10</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H60" s="2">
         <v>10.0</v>
@@ -18426,19 +18469,19 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H61" s="2">
         <v>10.0</v>
@@ -18449,7 +18492,7 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>23</v>
@@ -18461,7 +18504,7 @@
         <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="H62" s="2">
         <v>10.0</v>
@@ -18472,7 +18515,7 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>54</v>
@@ -18481,10 +18524,10 @@
         <v>10</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H63" s="2">
         <v>10.0</v>
@@ -18495,19 +18538,19 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H64" s="2">
         <v>10.0</v>
@@ -18518,19 +18561,19 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H65" s="2">
         <v>10.0</v>
@@ -18541,19 +18584,19 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H66" s="2">
         <v>10.0</v>
@@ -18564,19 +18607,19 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H67" s="2">
         <v>10.0</v>
@@ -18587,19 +18630,19 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H68" s="2">
         <v>10.0</v>
@@ -18610,19 +18653,19 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H69" s="2">
         <v>10.0</v>
@@ -18633,22 +18676,22 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="H70" s="2">
         <v>8.0</v>
@@ -18712,22 +18755,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H2" s="1">
         <v>4.0</v>
@@ -18738,22 +18781,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -18764,22 +18807,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -18790,22 +18833,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -18816,45 +18859,48 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7">
       <c r="A7" s="1">
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="H7" s="1">
         <v>4.0</v>
@@ -18865,22 +18911,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H8" s="1">
         <v>4.0</v>
@@ -18891,22 +18937,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H9" s="1">
         <v>4.0</v>
@@ -18917,22 +18963,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H10" s="1">
         <v>4.0</v>
@@ -18943,22 +18989,22 @@
         <v>12.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H11" s="2">
         <v>3.0</v>
@@ -18969,22 +19015,22 @@
         <v>31.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H12" s="2">
         <v>4.0</v>
@@ -18995,7 +19041,7 @@
         <v>78.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>62</v>
@@ -19007,10 +19053,10 @@
         <v>46</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -19021,10 +19067,10 @@
         <v>10.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
@@ -19033,10 +19079,10 @@
         <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H14" s="2">
         <v>9.0</v>
@@ -19047,10 +19093,10 @@
         <v>11.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
@@ -19059,10 +19105,10 @@
         <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H15" s="2">
         <v>6.0</v>
@@ -19073,10 +19119,10 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
@@ -19085,10 +19131,10 @@
         <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H16" s="2">
         <v>6.0</v>
@@ -19099,10 +19145,10 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
@@ -19122,10 +19168,10 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
@@ -19134,10 +19180,10 @@
         <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H18" s="2">
         <v>6.0</v>
@@ -19148,10 +19194,10 @@
         <v>16.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -19160,10 +19206,10 @@
         <v>11</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -19174,10 +19220,10 @@
         <v>17.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
@@ -19186,10 +19232,10 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -19200,10 +19246,10 @@
         <v>18.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
@@ -19212,10 +19258,10 @@
         <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -19226,10 +19272,10 @@
         <v>19.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -19238,10 +19284,10 @@
         <v>16</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -19252,10 +19298,10 @@
         <v>20.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -19264,10 +19310,10 @@
         <v>16</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H23" s="2">
         <v>6.0</v>
@@ -19278,10 +19324,10 @@
         <v>21.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
@@ -19301,10 +19347,10 @@
         <v>22.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
@@ -19324,10 +19370,10 @@
         <v>23.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>10</v>
@@ -19347,10 +19393,10 @@
         <v>24.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
@@ -19370,10 +19416,10 @@
         <v>25.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
@@ -19382,10 +19428,10 @@
         <v>16</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -19396,10 +19442,10 @@
         <v>26.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
@@ -19419,10 +19465,10 @@
         <v>27.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
@@ -19442,10 +19488,10 @@
         <v>28.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>10</v>
@@ -19465,10 +19511,10 @@
         <v>29.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>10</v>
@@ -19488,10 +19534,10 @@
         <v>30.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>10</v>
@@ -19500,10 +19546,10 @@
         <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -19514,7 +19560,7 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>59</v>
@@ -19537,7 +19583,7 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>31</v>
@@ -19560,10 +19606,10 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
@@ -19575,7 +19621,7 @@
         <v>12</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -19586,10 +19632,10 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>10</v>
@@ -19609,10 +19655,10 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>10</v>
@@ -19632,10 +19678,10 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>10</v>
@@ -19655,10 +19701,10 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>10</v>
@@ -19678,10 +19724,10 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>10</v>
@@ -19701,10 +19747,10 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>10</v>
@@ -19714,6 +19760,9 @@
       </c>
       <c r="F42" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="H42" s="2">
         <v>6.0</v>
@@ -19724,10 +19773,10 @@
         <v>41.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
@@ -19737,6 +19786,9 @@
       </c>
       <c r="F43" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="H43" s="2">
         <v>9.0</v>
@@ -19747,10 +19799,10 @@
         <v>42.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>10</v>
@@ -19770,7 +19822,7 @@
         <v>43.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>23</v>
@@ -19793,10 +19845,10 @@
         <v>44.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>10</v>
@@ -19806,6 +19858,9 @@
       </c>
       <c r="F46" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="H46" s="2">
         <v>6.0</v>
@@ -19816,10 +19871,10 @@
         <v>45.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>10</v>
@@ -19828,10 +19883,10 @@
         <v>38</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H47" s="2">
         <v>9.0</v>
@@ -19842,7 +19897,7 @@
         <v>46.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>59</v>
@@ -19854,10 +19909,10 @@
         <v>38</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -19868,7 +19923,7 @@
         <v>47.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>9</v>
@@ -19880,10 +19935,10 @@
         <v>38</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="H49" s="2">
         <v>6.0</v>
@@ -19894,10 +19949,10 @@
         <v>48.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>10</v>
@@ -19906,10 +19961,10 @@
         <v>38</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
@@ -19920,10 +19975,10 @@
         <v>49.0</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>10</v>
@@ -19932,10 +19987,10 @@
         <v>38</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="H51" s="2">
         <v>9.0</v>
@@ -19946,10 +20001,10 @@
         <v>50.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>10</v>
@@ -19958,10 +20013,10 @@
         <v>38</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="H52" s="2">
         <v>9.0</v>
@@ -19972,10 +20027,10 @@
         <v>51.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>10</v>
@@ -19995,10 +20050,10 @@
         <v>52.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>10</v>
@@ -20018,10 +20073,10 @@
         <v>53.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>10</v>
@@ -20041,10 +20096,10 @@
         <v>54.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>10</v>
@@ -20053,10 +20108,10 @@
         <v>38</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H56" s="2">
         <v>9.0</v>
@@ -20067,10 +20122,10 @@
         <v>55.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>10</v>
@@ -20090,10 +20145,10 @@
         <v>56.0</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>10</v>
@@ -20102,10 +20157,10 @@
         <v>46</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="H58" s="2">
         <v>9.0</v>
@@ -20116,10 +20171,10 @@
         <v>57.0</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>10</v>
@@ -20128,10 +20183,10 @@
         <v>46</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H59" s="2">
         <v>9.0</v>
@@ -20142,10 +20197,10 @@
         <v>58.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>10</v>
@@ -20157,7 +20212,7 @@
         <v>12</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H60" s="2">
         <v>9.0</v>
@@ -20168,10 +20223,10 @@
         <v>59.0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>10</v>
@@ -20183,7 +20238,7 @@
         <v>12</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="H61" s="2">
         <v>9.0</v>
@@ -20194,10 +20249,10 @@
         <v>60.0</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>10</v>
@@ -20206,10 +20261,10 @@
         <v>46</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="H62" s="2">
         <v>9.0</v>
@@ -20220,7 +20275,7 @@
         <v>61.0</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>73</v>
@@ -20232,10 +20287,10 @@
         <v>46</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H63" s="2">
         <v>9.0</v>
@@ -20246,7 +20301,7 @@
         <v>62.0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>77</v>
@@ -20261,7 +20316,7 @@
         <v>12</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H64" s="2">
         <v>9.0</v>
@@ -20272,10 +20327,10 @@
         <v>63.0</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>10</v>
@@ -20284,10 +20339,10 @@
         <v>46</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="H65" s="2">
         <v>9.0</v>
@@ -20298,10 +20353,10 @@
         <v>64.0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>10</v>
@@ -20313,7 +20368,7 @@
         <v>12</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H66" s="2">
         <v>9.0</v>
@@ -20324,10 +20379,10 @@
         <v>65.0</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>10</v>
@@ -20336,10 +20391,10 @@
         <v>46</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="H67" s="2">
         <v>9.0</v>
@@ -20350,10 +20405,10 @@
         <v>66.0</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>10</v>
@@ -20362,10 +20417,10 @@
         <v>46</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="H68" s="2">
         <v>9.0</v>
@@ -20376,10 +20431,10 @@
         <v>67.0</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>10</v>
@@ -20388,10 +20443,10 @@
         <v>46</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="H69" s="2">
         <v>9.0</v>
@@ -20402,7 +20457,7 @@
         <v>68.0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>42</v>
@@ -20414,10 +20469,10 @@
         <v>55</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="H70" s="2">
         <v>6.0</v>
@@ -20428,10 +20483,10 @@
         <v>69.0</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>10</v>
@@ -20440,10 +20495,10 @@
         <v>55</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="H71" s="2">
         <v>6.0</v>
@@ -20454,10 +20509,10 @@
         <v>70.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>10</v>
@@ -20466,10 +20521,10 @@
         <v>55</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="H72" s="2">
         <v>9.0</v>
@@ -20480,10 +20535,10 @@
         <v>71.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>10</v>
@@ -20492,10 +20547,10 @@
         <v>55</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="H73" s="2">
         <v>9.0</v>
@@ -20506,10 +20561,10 @@
         <v>72.0</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>10</v>
@@ -20529,10 +20584,10 @@
         <v>73.0</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>10</v>
@@ -20552,10 +20607,10 @@
         <v>74.0</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>10</v>
@@ -20564,10 +20619,10 @@
         <v>55</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H76" s="2">
         <v>6.0</v>
@@ -20578,10 +20633,10 @@
         <v>75.0</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>10</v>
@@ -20601,7 +20656,7 @@
         <v>76.0</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>37</v>
@@ -20624,10 +20679,10 @@
         <v>77.0</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>10</v>
@@ -20647,10 +20702,10 @@
         <v>78.0</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>10</v>
@@ -20659,10 +20714,10 @@
         <v>28</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="H80" s="2">
         <v>9.0</v>
@@ -20673,10 +20728,10 @@
         <v>79.0</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>10</v>
@@ -20685,10 +20740,10 @@
         <v>28</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="H81" s="2">
         <v>9.0</v>
@@ -20699,10 +20754,10 @@
         <v>80.0</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>10</v>
@@ -20714,7 +20769,7 @@
         <v>12</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="H82" s="2">
         <v>9.0</v>
@@ -20725,10 +20780,10 @@
         <v>81.0</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>10</v>
@@ -20740,7 +20795,7 @@
         <v>12</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="H83" s="2">
         <v>9.0</v>
@@ -20751,7 +20806,7 @@
         <v>82.0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>15</v>
@@ -20766,7 +20821,7 @@
         <v>12</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="H84" s="2">
         <v>4.0</v>
@@ -20777,10 +20832,10 @@
         <v>83.0</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>10</v>
@@ -20789,10 +20844,10 @@
         <v>16</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="H85" s="2">
         <v>9.0</v>
@@ -20803,10 +20858,10 @@
         <v>84.0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>10</v>
@@ -20815,10 +20870,10 @@
         <v>16</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="H86" s="2">
         <v>9.0</v>
@@ -20829,10 +20884,10 @@
         <v>85.0</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>10</v>
@@ -20841,10 +20896,10 @@
         <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="H87" s="2">
         <v>9.0</v>
@@ -20855,10 +20910,10 @@
         <v>86.0</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>10</v>
@@ -20867,10 +20922,10 @@
         <v>28</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H88" s="2">
         <v>9.0</v>
@@ -20881,10 +20936,10 @@
         <v>87.0</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>10</v>
@@ -20893,10 +20948,10 @@
         <v>38</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="H89" s="2">
         <v>9.0</v>
@@ -20907,7 +20962,7 @@
         <v>88.0</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>37</v>
@@ -20922,7 +20977,7 @@
         <v>12</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="H90" s="2">
         <v>9.0</v>
@@ -20933,10 +20988,10 @@
         <v>89.0</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>10</v>
@@ -21922,22 +21977,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -21948,22 +22003,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -21974,22 +22029,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -22000,22 +22055,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -22026,22 +22081,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="H6" s="1">
         <v>4.0</v>
@@ -22052,22 +22107,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="H7" s="2">
         <v>4.0</v>
@@ -22078,22 +22133,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H8" s="2">
         <v>7.0</v>
@@ -22104,22 +22159,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="H9" s="2">
         <v>7.0</v>
@@ -22130,22 +22185,22 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="H10" s="1">
         <v>5.0</v>
@@ -22156,10 +22211,10 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
@@ -22168,10 +22223,10 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -22182,10 +22237,10 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
@@ -22194,10 +22249,10 @@
         <v>55</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -22208,10 +22263,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -22220,10 +22275,10 @@
         <v>16</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="H13" s="2">
         <v>6.0</v>
@@ -22234,10 +22289,10 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>10</v>
@@ -22246,10 +22301,10 @@
         <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H14" s="2">
         <v>6.0</v>
@@ -22260,10 +22315,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
@@ -22272,10 +22327,10 @@
         <v>38</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -22286,10 +22341,10 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
@@ -22298,10 +22353,10 @@
         <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -22312,10 +22367,10 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
@@ -22324,10 +22379,10 @@
         <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="H17" s="2">
         <v>6.0</v>
@@ -22338,10 +22393,10 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
@@ -22350,10 +22405,10 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -22364,10 +22419,10 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -22376,10 +22431,10 @@
         <v>46</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="H19" s="1">
         <v>6.0</v>
@@ -22390,10 +22445,10 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>10</v>
@@ -22402,7 +22457,7 @@
         <v>16</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="H20" s="2">
         <v>9.0</v>
@@ -22413,10 +22468,10 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
@@ -22428,7 +22483,7 @@
         <v>12</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="H21" s="2">
         <v>9.0</v>
@@ -22439,10 +22494,10 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -22454,7 +22509,7 @@
         <v>12</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -22465,7 +22520,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>54</v>
@@ -22477,10 +22532,10 @@
         <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -22491,10 +22546,10 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
@@ -22503,10 +22558,10 @@
         <v>46</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -22517,10 +22572,10 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>10</v>
@@ -22529,10 +22584,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -22543,22 +22598,22 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="H26" s="2">
         <v>3.0</v>
@@ -22569,10 +22624,10 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
@@ -22581,10 +22636,10 @@
         <v>55</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
@@ -22595,10 +22650,10 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>10</v>
@@ -22607,10 +22662,10 @@
         <v>11</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="H28" s="2">
         <v>9.0</v>
@@ -22621,10 +22676,10 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>10</v>
@@ -22633,10 +22688,10 @@
         <v>55</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="H29" s="2">
         <v>9.0</v>
@@ -22647,10 +22702,10 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>10</v>
@@ -22659,10 +22714,10 @@
         <v>46</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="H30" s="2">
         <v>9.0</v>
@@ -22673,10 +22728,10 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -22688,7 +22743,7 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="H31" s="2">
         <v>9.0</v>
@@ -22699,10 +22754,10 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
@@ -22711,10 +22766,10 @@
         <v>38</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="H32" s="2">
         <v>9.0</v>
@@ -22725,10 +22780,10 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
@@ -22737,10 +22792,10 @@
         <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="H33" s="2">
         <v>9.0</v>
@@ -22751,7 +22806,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>31</v>
@@ -22763,10 +22818,10 @@
         <v>28</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="H34" s="2">
         <v>9.0</v>
@@ -22777,10 +22832,10 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
@@ -22789,10 +22844,10 @@
         <v>55</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H35" s="2">
         <v>9.0</v>
@@ -22803,10 +22858,10 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
@@ -22815,10 +22870,10 @@
         <v>55</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="H36" s="2">
         <v>9.0</v>
@@ -22829,10 +22884,10 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
@@ -22841,10 +22896,10 @@
         <v>16</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="H37" s="2">
         <v>9.0</v>
@@ -22855,10 +22910,10 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
@@ -22867,7 +22922,7 @@
         <v>16</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="H38" s="2">
         <v>9.0</v>
@@ -22878,10 +22933,10 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
@@ -22890,10 +22945,10 @@
         <v>46</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="H39" s="2">
         <v>9.0</v>
@@ -22904,10 +22959,10 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
@@ -22916,10 +22971,10 @@
         <v>46</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="H40" s="2">
         <v>9.0</v>
@@ -22930,10 +22985,10 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
@@ -22942,10 +22997,10 @@
         <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="H41" s="2">
         <v>9.0</v>
@@ -22956,10 +23011,10 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
@@ -22968,10 +23023,10 @@
         <v>11</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="H42" s="2">
         <v>9.0</v>
@@ -22982,7 +23037,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>27</v>
@@ -22994,10 +23049,10 @@
         <v>16</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="H43" s="2">
         <v>9.0</v>
@@ -23008,7 +23063,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>88</v>
@@ -23020,7 +23075,7 @@
         <v>55</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H44" s="2">
         <v>9.0</v>
@@ -23031,7 +23086,7 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>88</v>
@@ -23043,10 +23098,10 @@
         <v>38</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="H45" s="2">
         <v>6.0</v>
@@ -23057,10 +23112,10 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
@@ -23069,10 +23124,10 @@
         <v>11</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="H46" s="2">
         <v>9.0</v>
@@ -23083,7 +23138,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>66</v>
@@ -23095,7 +23150,7 @@
         <v>46</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="H47" s="2">
         <v>6.0</v>
@@ -23106,10 +23161,10 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
@@ -23118,10 +23173,10 @@
         <v>16</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H48" s="2">
         <v>9.0</v>
@@ -23132,10 +23187,10 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
@@ -23144,10 +23199,10 @@
         <v>28</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="H49" s="2">
         <v>9.0</v>
@@ -23158,10 +23213,10 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
@@ -23170,41 +23225,16 @@
         <v>28</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="H50" s="2">
         <v>9.0</v>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="2">
-        <v>50.0</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="H51" s="2">
-        <v>4.0</v>
-      </c>
-    </row>
+    <row r="51" ht="15.75" customHeight="1"/>
     <row r="52" ht="15.75" customHeight="1"/>
     <row r="53" ht="15.75" customHeight="1"/>
     <row r="54" ht="15.75" customHeight="1"/>
@@ -24214,22 +24244,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="H2" s="2">
         <v>5.0</v>
@@ -24240,22 +24270,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="H3" s="1">
         <v>4.0</v>
@@ -24266,22 +24296,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -24292,22 +24322,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -24318,22 +24348,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H6" s="2">
         <v>5.0</v>
@@ -24344,22 +24374,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -24370,22 +24400,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>543</v>
+      <c r="F8" s="5" t="s">
+        <v>545</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H8" s="2">
         <v>4.0</v>
@@ -24396,22 +24426,22 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="H9" s="2">
         <v>6.0</v>
@@ -24422,10 +24452,10 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
@@ -24434,10 +24464,10 @@
         <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -24448,10 +24478,10 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
@@ -24460,10 +24490,10 @@
         <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H11" s="2">
         <v>6.0</v>
@@ -24474,22 +24504,22 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H12" s="2">
         <v>5.0</v>
@@ -24500,22 +24530,22 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H13" s="2">
         <v>3.0</v>
@@ -24526,7 +24556,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>59</v>
@@ -24538,7 +24568,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H14" s="1">
         <v>6.0</v>
@@ -24549,10 +24579,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
@@ -24561,10 +24591,10 @@
         <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H15" s="2">
         <v>9.0</v>
@@ -24575,10 +24605,10 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>10</v>
@@ -24587,10 +24617,10 @@
         <v>38</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="H16" s="2">
         <v>9.0</v>
@@ -24601,10 +24631,10 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>10</v>
@@ -24613,10 +24643,10 @@
         <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H17" s="2">
         <v>9.0</v>
@@ -24627,10 +24657,10 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>10</v>
@@ -24639,10 +24669,10 @@
         <v>46</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H18" s="2">
         <v>9.0</v>
@@ -24653,10 +24683,10 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -24665,10 +24695,10 @@
         <v>38</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="H19" s="2">
         <v>9.0</v>
@@ -24679,22 +24709,22 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H20" s="2">
         <v>7.0</v>
@@ -24705,10 +24735,10 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>10</v>
@@ -24717,10 +24747,10 @@
         <v>38</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H21" s="2">
         <v>7.0</v>
@@ -24731,10 +24761,10 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>10</v>
@@ -24743,10 +24773,10 @@
         <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H22" s="2">
         <v>9.0</v>
@@ -24757,10 +24787,10 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -24769,7 +24799,7 @@
         <v>55</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H23" s="2">
         <v>9.0</v>
@@ -24780,10 +24810,10 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>10</v>
@@ -24792,10 +24822,10 @@
         <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H24" s="2">
         <v>9.0</v>
@@ -24806,10 +24836,10 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -24818,10 +24848,10 @@
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="H25" s="2">
         <v>9.0</v>
@@ -24832,10 +24862,10 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -24844,10 +24874,10 @@
         <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H26" s="2">
         <v>9.0</v>
@@ -24858,10 +24888,10 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
@@ -24870,16 +24900,41 @@
         <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="H27" s="2">
         <v>9.0</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="H28" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
     <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -25912,7 +25967,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>54</v>
@@ -25924,10 +25979,10 @@
         <v>38</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="H2" s="2">
         <v>6.0</v>
@@ -25938,22 +25993,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="H3" s="2">
         <v>7.0</v>
@@ -25964,22 +26019,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="H4" s="2">
         <v>7.0</v>
@@ -25990,22 +26045,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="H5" s="1">
         <v>4.0</v>
@@ -26016,22 +26071,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -26042,22 +26097,22 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="H7" s="1">
         <v>5.0</v>
@@ -26068,7 +26123,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>59</v>
@@ -26080,7 +26135,7 @@
         <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H8" s="2">
         <v>6.0</v>
@@ -26091,10 +26146,10 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
@@ -26103,10 +26158,10 @@
         <v>55</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -26117,7 +26172,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>59</v>
@@ -26129,7 +26184,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H10" s="2">
         <v>6.0</v>
@@ -27181,22 +27236,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="H2" s="2">
         <v>2.0</v>
@@ -27207,22 +27262,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>637</v>
+      <c r="F3" s="4" t="s">
+        <v>642</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -27233,22 +27288,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -27259,22 +27314,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>644</v>
+        <v>648</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>649</v>
       </c>
       <c r="H5" s="1">
         <v>5.0</v>
@@ -27285,22 +27340,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>647</v>
+        <v>651</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>652</v>
       </c>
       <c r="H6" s="1">
         <v>5.0</v>
@@ -27311,10 +27366,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -27322,11 +27377,11 @@
       <c r="E7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>649</v>
+      <c r="F7" s="5" t="s">
+        <v>654</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>
@@ -27337,10 +27392,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>10</v>
@@ -27349,7 +27404,7 @@
         <v>55</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H8" s="2">
         <v>9.0</v>
@@ -27360,10 +27415,10 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
@@ -27372,10 +27427,10 @@
         <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="H9" s="2">
         <v>9.0</v>
@@ -27386,10 +27441,10 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>10</v>
@@ -27398,7 +27453,7 @@
         <v>55</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H10" s="2">
         <v>9.0</v>
@@ -27409,10 +27464,10 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
@@ -27421,10 +27476,10 @@
         <v>38</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="H11" s="2">
         <v>9.0</v>
@@ -27435,10 +27490,10 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
@@ -27447,10 +27502,10 @@
         <v>55</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="H12" s="2">
         <v>9.0</v>
@@ -27461,10 +27516,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -27473,10 +27528,10 @@
         <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="H13" s="2">
         <v>9.0</v>
@@ -28524,22 +28579,22 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="H2" s="2">
         <v>3.0</v>
@@ -28550,22 +28605,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="H3" s="1">
         <v>5.0</v>
@@ -28576,22 +28631,22 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="H4" s="1">
         <v>5.0</v>
@@ -28602,10 +28657,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -28614,7 +28669,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H5" s="2">
         <v>9.0</v>
@@ -28625,10 +28680,10 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
@@ -28637,10 +28692,10 @@
         <v>55</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="H6" s="2">
         <v>9.0</v>
@@ -28651,10 +28706,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -28663,10 +28718,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="H7" s="2">
         <v>6.0</v>
@@ -28677,22 +28732,22 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="H8" s="2">
         <v>5.0</v>
@@ -29746,10 +29801,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -29758,10 +29813,10 @@
         <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="H2" s="2">
         <v>9.0</v>
@@ -29772,22 +29827,22 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="H3" s="2">
         <v>9.0</v>
@@ -29798,10 +29853,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
@@ -29810,7 +29865,7 @@
         <v>46</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="H4" s="2">
         <v>9.0</v>
@@ -29821,22 +29876,22 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="H5" s="2">
         <v>5.0</v>
@@ -29847,22 +29902,22 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="H6" s="2">
         <v>7.0</v>
@@ -29873,10 +29928,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
@@ -29885,10 +29940,10 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="H7" s="2">
         <v>9.0</v>
